--- a/apps/api/data/excel_templates/countries.xlsx
+++ b/apps/api/data/excel_templates/countries.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valentindaveau/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valentindaveau/Bildix/Website/Bildyx/apps/api/data/excel_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAAFA9DC-447C-6044-BD46-85D86C384B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FA9AE5-3542-0543-ABB8-15D5BD614500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="20740" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="countries" sheetId="1" r:id="rId1"/>
@@ -8615,9 +8615,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$€-2]\ #,##0;[Red]\-[$€-2]\ #,##0"/>
-  </numFmts>
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -8676,7 +8673,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -8694,13 +8691,17 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -9008,9 +9009,13 @@
   <dimension ref="A1:AV101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="11" width="18" customWidth="1"/>
+    <col min="1" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="32.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18" style="9" customWidth="1"/>
+    <col min="8" max="8" width="18" style="12" customWidth="1"/>
+    <col min="9" max="9" width="22" style="12" customWidth="1"/>
+    <col min="10" max="10" width="18" style="12" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
     <col min="12" max="12" width="21" customWidth="1"/>
     <col min="13" max="13" width="18" customWidth="1"/>
     <col min="14" max="15" width="19" customWidth="1"/>
@@ -9018,26 +9023,29 @@
     <col min="19" max="20" width="21" customWidth="1"/>
     <col min="21" max="21" width="19" customWidth="1"/>
     <col min="22" max="22" width="31" customWidth="1"/>
-    <col min="23" max="24" width="18" customWidth="1"/>
-    <col min="25" max="25" width="21" customWidth="1"/>
-    <col min="26" max="26" width="18" customWidth="1"/>
+    <col min="23" max="23" width="18" style="9" customWidth="1"/>
+    <col min="24" max="24" width="18" customWidth="1"/>
+    <col min="25" max="25" width="21" style="9" customWidth="1"/>
+    <col min="26" max="26" width="18" style="9" customWidth="1"/>
     <col min="27" max="27" width="20" customWidth="1"/>
     <col min="28" max="28" width="23" customWidth="1"/>
     <col min="29" max="29" width="18" customWidth="1"/>
     <col min="30" max="30" width="32" customWidth="1"/>
     <col min="31" max="31" width="26" customWidth="1"/>
-    <col min="32" max="32" width="36" customWidth="1"/>
-    <col min="33" max="33" width="35" customWidth="1"/>
+    <col min="32" max="32" width="36" style="9" customWidth="1"/>
+    <col min="33" max="33" width="35" style="9" customWidth="1"/>
     <col min="34" max="34" width="23" customWidth="1"/>
     <col min="35" max="36" width="22" customWidth="1"/>
     <col min="37" max="37" width="24" customWidth="1"/>
     <col min="38" max="38" width="18" customWidth="1"/>
-    <col min="39" max="39" width="26" customWidth="1"/>
+    <col min="39" max="39" width="26" style="9" customWidth="1"/>
     <col min="40" max="40" width="20" customWidth="1"/>
     <col min="41" max="42" width="18" customWidth="1"/>
     <col min="43" max="43" width="19" customWidth="1"/>
-    <col min="44" max="44" width="22" customWidth="1"/>
+    <col min="44" max="44" width="103.1640625" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="18" customWidth="1"/>
+    <col min="47" max="47" width="40.5" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="71.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:48">
@@ -9059,16 +9067,16 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -9107,16 +9115,16 @@
       <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="7" t="s">
         <v>22</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="7" t="s">
         <v>25</v>
       </c>
       <c r="AA1" s="1" t="s">
@@ -9134,10 +9142,10 @@
       <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" s="7" t="s">
         <v>32</v>
       </c>
       <c r="AH1" s="1" t="s">
@@ -9155,7 +9163,7 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" s="7" t="s">
         <v>38</v>
       </c>
       <c r="AN1" s="1" t="s">
@@ -9190,6 +9198,10 @@
       <c r="F2" s="3" t="s">
         <v>2256</v>
       </c>
+      <c r="G2" s="8"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
       <c r="K2" s="2" t="s">
         <v>2255</v>
       </c>
@@ -9220,16 +9232,16 @@
       <c r="V2" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" s="8" t="s">
         <v>413</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Y2" s="8" t="s">
         <v>640</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="Z2" s="8" t="s">
         <v>464</v>
       </c>
       <c r="AA2" s="4" t="s">
@@ -9247,10 +9259,10 @@
       <c r="AE2" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF2" s="4" t="s">
+      <c r="AF2" s="13" t="s">
         <v>589</v>
       </c>
-      <c r="AG2" s="4" t="s">
+      <c r="AG2" s="13" t="s">
         <v>791</v>
       </c>
       <c r="AH2" s="2" t="s">
@@ -9268,7 +9280,7 @@
       <c r="AL2" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AM2" s="8" t="s">
         <v>585</v>
       </c>
       <c r="AN2" s="2" t="s">
@@ -9306,6 +9318,10 @@
       <c r="F3" s="3" t="s">
         <v>2240</v>
       </c>
+      <c r="G3" s="8"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
       <c r="K3" s="2" t="s">
         <v>2239</v>
       </c>
@@ -9336,16 +9352,16 @@
       <c r="V3" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="W3" s="8" t="s">
         <v>331</v>
       </c>
       <c r="X3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="Y3" s="8" t="s">
         <v>1623</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="Z3" s="8" t="s">
         <v>1622</v>
       </c>
       <c r="AA3" s="4" t="s">
@@ -9363,10 +9379,10 @@
       <c r="AE3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AF3" s="4" t="s">
+      <c r="AF3" s="13" t="s">
         <v>2234</v>
       </c>
-      <c r="AG3" s="4" t="s">
+      <c r="AG3" s="13" t="s">
         <v>93</v>
       </c>
       <c r="AH3" s="2" t="s">
@@ -9384,7 +9400,7 @@
       <c r="AL3" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="AM3" s="2" t="s">
+      <c r="AM3" s="8" t="s">
         <v>951</v>
       </c>
       <c r="AN3" s="2" t="s">
@@ -9422,6 +9438,10 @@
       <c r="F4" s="3" t="s">
         <v>2224</v>
       </c>
+      <c r="G4" s="8"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
       <c r="K4" s="2" t="s">
         <v>2223</v>
       </c>
@@ -9452,16 +9472,16 @@
       <c r="V4" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="W4" s="2" t="s">
+      <c r="W4" s="8" t="s">
         <v>2218</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y4" s="2" t="s">
+      <c r="Y4" s="8" t="s">
         <v>770</v>
       </c>
-      <c r="Z4" s="2" t="s">
+      <c r="Z4" s="8" t="s">
         <v>2217</v>
       </c>
       <c r="AA4" s="4" t="s">
@@ -9479,10 +9499,10 @@
       <c r="AE4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AF4" s="4" t="s">
+      <c r="AF4" s="13" t="s">
         <v>1123</v>
       </c>
-      <c r="AG4" s="4" t="s">
+      <c r="AG4" s="13" t="s">
         <v>408</v>
       </c>
       <c r="AH4" s="2" t="s">
@@ -9500,7 +9520,7 @@
       <c r="AL4" s="2" t="s">
         <v>2212</v>
       </c>
-      <c r="AM4" s="2" t="s">
+      <c r="AM4" s="8" t="s">
         <v>2211</v>
       </c>
       <c r="AN4" s="2" t="s">
@@ -9538,6 +9558,10 @@
       <c r="F5" s="3" t="s">
         <v>2200</v>
       </c>
+      <c r="G5" s="8"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
       <c r="K5" s="2" t="s">
         <v>2078</v>
       </c>
@@ -9568,16 +9592,16 @@
       <c r="V5" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="W5" s="2" t="s">
+      <c r="W5" s="8" t="s">
         <v>2195</v>
       </c>
       <c r="X5" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y5" s="2" t="s">
+      <c r="Y5" s="8" t="s">
         <v>2194</v>
       </c>
-      <c r="Z5" s="2" t="s">
+      <c r="Z5" s="8" t="s">
         <v>2193</v>
       </c>
       <c r="AA5" s="4" t="s">
@@ -9595,10 +9619,10 @@
       <c r="AE5" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="AF5" s="4" t="s">
+      <c r="AF5" s="13" t="s">
         <v>2191</v>
       </c>
-      <c r="AG5" s="4" t="s">
+      <c r="AG5" s="13" t="s">
         <v>1101</v>
       </c>
       <c r="AH5" s="2" t="s">
@@ -9616,7 +9640,7 @@
       <c r="AL5" s="2" t="s">
         <v>2189</v>
       </c>
-      <c r="AM5" s="2" t="s">
+      <c r="AM5" s="8" t="s">
         <v>241</v>
       </c>
       <c r="AN5" s="2" t="s">
@@ -9654,6 +9678,10 @@
       <c r="F6" s="3" t="s">
         <v>2178</v>
       </c>
+      <c r="G6" s="8"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
       <c r="K6" s="2" t="s">
         <v>2177</v>
       </c>
@@ -9684,16 +9712,16 @@
       <c r="V6" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W6" s="2" t="s">
+      <c r="W6" s="8" t="s">
         <v>465</v>
       </c>
       <c r="X6" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y6" s="2" t="s">
+      <c r="Y6" s="8" t="s">
         <v>617</v>
       </c>
-      <c r="Z6" s="2" t="s">
+      <c r="Z6" s="8" t="s">
         <v>166</v>
       </c>
       <c r="AA6" s="4" t="s">
@@ -9711,10 +9739,10 @@
       <c r="AE6" s="4" t="s">
         <v>792</v>
       </c>
-      <c r="AF6" s="4" t="s">
+      <c r="AF6" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="AG6" s="4" t="s">
+      <c r="AG6" s="13" t="s">
         <v>190</v>
       </c>
       <c r="AH6" s="2" t="s">
@@ -9732,7 +9760,7 @@
       <c r="AL6" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="AM6" s="2" t="s">
+      <c r="AM6" s="8" t="s">
         <v>951</v>
       </c>
       <c r="AN6" s="2" t="s">
@@ -9770,6 +9798,10 @@
       <c r="F7" s="3" t="s">
         <v>2159</v>
       </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
       <c r="K7" s="2" t="s">
         <v>2158</v>
       </c>
@@ -9800,16 +9832,16 @@
       <c r="V7" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="W7" s="8" t="s">
         <v>2152</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y7" s="2" t="s">
+      <c r="Y7" s="8" t="s">
         <v>685</v>
       </c>
-      <c r="Z7" s="2" t="s">
+      <c r="Z7" s="8" t="s">
         <v>565</v>
       </c>
       <c r="AA7" s="4" t="s">
@@ -9827,10 +9859,10 @@
       <c r="AE7" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF7" s="4" t="s">
+      <c r="AF7" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="AG7" s="4" t="s">
+      <c r="AG7" s="13" t="s">
         <v>909</v>
       </c>
       <c r="AH7" s="2" t="s">
@@ -9848,7 +9880,7 @@
       <c r="AL7" s="2" t="s">
         <v>1369</v>
       </c>
-      <c r="AM7" s="2" t="s">
+      <c r="AM7" s="8" t="s">
         <v>282</v>
       </c>
       <c r="AN7" s="2" t="s">
@@ -9886,6 +9918,10 @@
       <c r="F8" s="3" t="s">
         <v>2140</v>
       </c>
+      <c r="G8" s="8"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
       <c r="K8" s="2" t="s">
         <v>76</v>
       </c>
@@ -9916,16 +9952,16 @@
       <c r="V8" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="W8" s="2" t="s">
+      <c r="W8" s="8" t="s">
         <v>2135</v>
       </c>
       <c r="X8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y8" s="2" t="s">
+      <c r="Y8" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="Z8" s="2" t="s">
+      <c r="Z8" s="8" t="s">
         <v>438</v>
       </c>
       <c r="AA8" s="4" t="s">
@@ -9943,10 +9979,10 @@
       <c r="AE8" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="AF8" s="4" t="s">
+      <c r="AF8" s="13" t="s">
         <v>2132</v>
       </c>
-      <c r="AG8" s="4" t="s">
+      <c r="AG8" s="13" t="s">
         <v>329</v>
       </c>
       <c r="AH8" s="2" t="s">
@@ -9964,7 +10000,7 @@
       <c r="AL8" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="AM8" s="2" t="s">
+      <c r="AM8" s="8" t="s">
         <v>441</v>
       </c>
       <c r="AN8" s="2" t="s">
@@ -10002,6 +10038,10 @@
       <c r="F9" s="3" t="s">
         <v>2119</v>
       </c>
+      <c r="G9" s="8"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
       <c r="K9" s="2" t="s">
         <v>2118</v>
       </c>
@@ -10032,16 +10072,16 @@
       <c r="V9" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="W9" s="2" t="s">
+      <c r="W9" s="8" t="s">
         <v>2113</v>
       </c>
       <c r="X9" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="Y9" s="2" t="s">
+      <c r="Y9" s="8" t="s">
         <v>2112</v>
       </c>
-      <c r="Z9" s="2" t="s">
+      <c r="Z9" s="8" t="s">
         <v>2111</v>
       </c>
       <c r="AA9" s="4" t="s">
@@ -10059,10 +10099,10 @@
       <c r="AE9" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AF9" s="4" t="s">
+      <c r="AF9" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="AG9" s="4" t="s">
+      <c r="AG9" s="13" t="s">
         <v>706</v>
       </c>
       <c r="AH9" s="2" t="s">
@@ -10080,7 +10120,7 @@
       <c r="AL9" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="AM9" s="2" t="s">
+      <c r="AM9" s="8" t="s">
         <v>243</v>
       </c>
       <c r="AN9" s="2" t="s">
@@ -10118,6 +10158,10 @@
       <c r="F10" s="3" t="s">
         <v>2098</v>
       </c>
+      <c r="G10" s="8"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
       <c r="K10" s="2" t="s">
         <v>2097</v>
       </c>
@@ -10148,16 +10192,16 @@
       <c r="V10" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="W10" s="2" t="s">
+      <c r="W10" s="8" t="s">
         <v>2093</v>
       </c>
       <c r="X10" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y10" s="2" t="s">
+      <c r="Y10" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="Z10" s="2" t="s">
+      <c r="Z10" s="8" t="s">
         <v>464</v>
       </c>
       <c r="AA10" s="4" t="s">
@@ -10175,10 +10219,10 @@
       <c r="AE10" s="4" t="s">
         <v>638</v>
       </c>
-      <c r="AF10" s="4" t="s">
+      <c r="AF10" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="AG10" s="4" t="s">
+      <c r="AG10" s="13" t="s">
         <v>332</v>
       </c>
       <c r="AH10" s="2" t="s">
@@ -10196,7 +10240,7 @@
       <c r="AL10" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="AM10" s="2">
+      <c r="AM10" s="8">
         <v>5</v>
       </c>
       <c r="AN10" s="2" t="s">
@@ -10234,6 +10278,10 @@
       <c r="F11" s="3" t="s">
         <v>2079</v>
       </c>
+      <c r="G11" s="8"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
       <c r="K11" s="2" t="s">
         <v>2078</v>
       </c>
@@ -10264,16 +10312,16 @@
       <c r="V11" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W11" s="2" t="s">
+      <c r="W11" s="8" t="s">
         <v>2072</v>
       </c>
       <c r="X11" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="Y11" s="2" t="s">
+      <c r="Y11" s="8" t="s">
         <v>2071</v>
       </c>
-      <c r="Z11" s="2" t="s">
+      <c r="Z11" s="8" t="s">
         <v>2070</v>
       </c>
       <c r="AA11" s="4" t="s">
@@ -10291,10 +10339,10 @@
       <c r="AE11" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="AF11" s="4" t="s">
+      <c r="AF11" s="13" t="s">
         <v>408</v>
       </c>
-      <c r="AG11" s="4" t="s">
+      <c r="AG11" s="13" t="s">
         <v>637</v>
       </c>
       <c r="AH11" s="2" t="s">
@@ -10312,7 +10360,7 @@
       <c r="AL11" s="2" t="s">
         <v>2065</v>
       </c>
-      <c r="AM11" s="2">
+      <c r="AM11" s="8">
         <v>45691</v>
       </c>
       <c r="AN11" s="2" t="s">
@@ -10350,6 +10398,10 @@
       <c r="F12" s="3" t="s">
         <v>2054</v>
       </c>
+      <c r="G12" s="8"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
       <c r="K12" s="2" t="s">
         <v>2053</v>
       </c>
@@ -10380,16 +10432,16 @@
       <c r="V12" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="W12" s="2" t="s">
+      <c r="W12" s="8" t="s">
         <v>1142</v>
       </c>
       <c r="X12" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y12" s="2" t="s">
+      <c r="Y12" s="8" t="s">
         <v>541</v>
       </c>
-      <c r="Z12" s="2" t="s">
+      <c r="Z12" s="8" t="s">
         <v>385</v>
       </c>
       <c r="AA12" s="4" t="s">
@@ -10407,10 +10459,10 @@
       <c r="AE12" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF12" s="4" t="s">
+      <c r="AF12" s="13" t="s">
         <v>486</v>
       </c>
-      <c r="AG12" s="4" t="s">
+      <c r="AG12" s="13" t="s">
         <v>191</v>
       </c>
       <c r="AH12" s="2" t="s">
@@ -10428,7 +10480,7 @@
       <c r="AL12" s="2" t="s">
         <v>1369</v>
       </c>
-      <c r="AM12" s="2" t="s">
+      <c r="AM12" s="8" t="s">
         <v>241</v>
       </c>
       <c r="AN12" s="2" t="s">
@@ -10466,6 +10518,10 @@
       <c r="F13" s="3" t="s">
         <v>2036</v>
       </c>
+      <c r="G13" s="8"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
       <c r="K13" s="2" t="s">
         <v>2035</v>
       </c>
@@ -10496,16 +10552,16 @@
       <c r="V13" s="2" t="s">
         <v>1542</v>
       </c>
-      <c r="W13" s="2" t="s">
+      <c r="W13" s="8" t="s">
         <v>2030</v>
       </c>
       <c r="X13" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="Y13" s="2" t="s">
+      <c r="Y13" s="8" t="s">
         <v>2029</v>
       </c>
-      <c r="Z13" s="2" t="s">
+      <c r="Z13" s="8" t="s">
         <v>2028</v>
       </c>
       <c r="AA13" s="4" t="s">
@@ -10523,10 +10579,10 @@
       <c r="AE13" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="AF13" s="4" t="s">
+      <c r="AF13" s="13" t="s">
         <v>2025</v>
       </c>
-      <c r="AG13" s="4" t="s">
+      <c r="AG13" s="13" t="s">
         <v>1123</v>
       </c>
       <c r="AH13" s="2" t="s">
@@ -10544,7 +10600,7 @@
       <c r="AL13" s="2" t="s">
         <v>1638</v>
       </c>
-      <c r="AM13" s="2" t="s">
+      <c r="AM13" s="8" t="s">
         <v>243</v>
       </c>
       <c r="AN13" s="2" t="s">
@@ -10582,6 +10638,10 @@
       <c r="F14" s="3" t="s">
         <v>2001</v>
       </c>
+      <c r="G14" s="8"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
       <c r="K14" s="2" t="s">
         <v>2014</v>
       </c>
@@ -10612,16 +10672,16 @@
       <c r="V14" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W14" s="2" t="s">
+      <c r="W14" s="8" t="s">
         <v>2011</v>
       </c>
       <c r="X14" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y14" s="2" t="s">
+      <c r="Y14" s="8" t="s">
         <v>770</v>
       </c>
-      <c r="Z14" s="2" t="s">
+      <c r="Z14" s="8" t="s">
         <v>769</v>
       </c>
       <c r="AA14" s="4" t="s">
@@ -10639,10 +10699,10 @@
       <c r="AE14" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF14" s="4" t="s">
+      <c r="AF14" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="AG14" s="4" t="s">
+      <c r="AG14" s="13" t="s">
         <v>791</v>
       </c>
       <c r="AH14" s="2" t="s">
@@ -10660,7 +10720,7 @@
       <c r="AL14" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="AM14" s="2" t="s">
+      <c r="AM14" s="8" t="s">
         <v>241</v>
       </c>
       <c r="AN14" s="2" t="s">
@@ -10698,6 +10758,10 @@
       <c r="F15" s="3" t="s">
         <v>2001</v>
       </c>
+      <c r="G15" s="8"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
       <c r="K15" s="2" t="s">
         <v>2000</v>
       </c>
@@ -10728,16 +10792,16 @@
       <c r="V15" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W15" s="2" t="s">
+      <c r="W15" s="8" t="s">
         <v>387</v>
       </c>
       <c r="X15" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="Y15" s="2" t="s">
+      <c r="Y15" s="8" t="s">
         <v>640</v>
       </c>
-      <c r="Z15" s="2" t="s">
+      <c r="Z15" s="8" t="s">
         <v>464</v>
       </c>
       <c r="AA15" s="4" t="s">
@@ -10755,10 +10819,10 @@
       <c r="AE15" s="4" t="s">
         <v>792</v>
       </c>
-      <c r="AF15" s="4" t="s">
+      <c r="AF15" s="13" t="s">
         <v>791</v>
       </c>
-      <c r="AG15" s="4" t="s">
+      <c r="AG15" s="13" t="s">
         <v>790</v>
       </c>
       <c r="AH15" s="2" t="s">
@@ -10776,7 +10840,7 @@
       <c r="AL15" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="AM15" s="2" t="s">
+      <c r="AM15" s="8" t="s">
         <v>243</v>
       </c>
       <c r="AN15" s="2" t="s">
@@ -10814,6 +10878,10 @@
       <c r="F16" s="3" t="s">
         <v>1985</v>
       </c>
+      <c r="G16" s="8"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
       <c r="K16" s="2" t="s">
         <v>1984</v>
       </c>
@@ -10844,16 +10912,16 @@
       <c r="V16" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W16" s="2" t="s">
+      <c r="W16" s="8" t="s">
         <v>167</v>
       </c>
       <c r="X16" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="Y16" s="2" t="s">
+      <c r="Y16" s="8" t="s">
         <v>1979</v>
       </c>
-      <c r="Z16" s="2" t="s">
+      <c r="Z16" s="8" t="s">
         <v>1020</v>
       </c>
       <c r="AA16" s="4" t="s">
@@ -10871,10 +10939,10 @@
       <c r="AE16" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AF16" s="4" t="s">
+      <c r="AF16" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="AG16" s="4" t="s">
+      <c r="AG16" s="13" t="s">
         <v>791</v>
       </c>
       <c r="AH16" s="2" t="s">
@@ -10892,7 +10960,7 @@
       <c r="AL16" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="AM16" s="2">
+      <c r="AM16" s="8">
         <v>2</v>
       </c>
       <c r="AN16" s="2" t="s">
@@ -10930,6 +10998,10 @@
       <c r="F17" s="3" t="s">
         <v>1964</v>
       </c>
+      <c r="G17" s="8"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
       <c r="K17" s="2" t="s">
         <v>76</v>
       </c>
@@ -10960,16 +11032,16 @@
       <c r="V17" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="W17" s="2" t="s">
+      <c r="W17" s="8" t="s">
         <v>281</v>
       </c>
       <c r="X17" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y17" s="2" t="s">
+      <c r="Y17" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="Z17" s="2" t="s">
+      <c r="Z17" s="8" t="s">
         <v>438</v>
       </c>
       <c r="AA17" s="4" t="s">
@@ -10987,10 +11059,10 @@
       <c r="AE17" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="AF17" s="4" t="s">
+      <c r="AF17" s="13" t="s">
         <v>1957</v>
       </c>
-      <c r="AG17" s="4" t="s">
+      <c r="AG17" s="13" t="s">
         <v>58</v>
       </c>
       <c r="AH17" s="2" t="s">
@@ -11008,7 +11080,7 @@
       <c r="AL17" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="AM17" s="2" t="s">
+      <c r="AM17" s="8" t="s">
         <v>254</v>
       </c>
       <c r="AN17" s="2" t="s">
@@ -11046,6 +11118,10 @@
       <c r="F18" s="3" t="s">
         <v>1944</v>
       </c>
+      <c r="G18" s="8"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
       <c r="K18" s="2" t="s">
         <v>1943</v>
       </c>
@@ -11076,16 +11152,16 @@
       <c r="V18" s="2" t="s">
         <v>1308</v>
       </c>
-      <c r="W18" s="2" t="s">
+      <c r="W18" s="8" t="s">
         <v>1939</v>
       </c>
       <c r="X18" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y18" s="2" t="s">
+      <c r="Y18" s="8" t="s">
         <v>1938</v>
       </c>
-      <c r="Z18" s="2" t="s">
+      <c r="Z18" s="8" t="s">
         <v>1937</v>
       </c>
       <c r="AA18" s="4" t="s">
@@ -11103,10 +11179,10 @@
       <c r="AE18" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AF18" s="4" t="s">
+      <c r="AF18" s="13" t="s">
         <v>1934</v>
       </c>
-      <c r="AG18" s="4" t="s">
+      <c r="AG18" s="13" t="s">
         <v>276</v>
       </c>
       <c r="AH18" s="2" t="s">
@@ -11124,7 +11200,7 @@
       <c r="AL18" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="AM18" s="2" t="s">
+      <c r="AM18" s="8" t="s">
         <v>157</v>
       </c>
       <c r="AN18" s="2" t="s">
@@ -11162,6 +11238,10 @@
       <c r="F19" s="3" t="s">
         <v>1922</v>
       </c>
+      <c r="G19" s="8"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
       <c r="K19" s="2" t="s">
         <v>76</v>
       </c>
@@ -11192,16 +11272,16 @@
       <c r="V19" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="W19" s="2" t="s">
+      <c r="W19" s="8" t="s">
         <v>1644</v>
       </c>
       <c r="X19" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y19" s="2" t="s">
+      <c r="Y19" s="8" t="s">
         <v>1916</v>
       </c>
-      <c r="Z19" s="2" t="s">
+      <c r="Z19" s="8" t="s">
         <v>1915</v>
       </c>
       <c r="AA19" s="4" t="s">
@@ -11219,10 +11299,10 @@
       <c r="AE19" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AF19" s="4" t="s">
+      <c r="AF19" s="13" t="s">
         <v>929</v>
       </c>
-      <c r="AG19" s="4" t="s">
+      <c r="AG19" s="13" t="s">
         <v>909</v>
       </c>
       <c r="AH19" s="2" t="s">
@@ -11240,7 +11320,7 @@
       <c r="AL19" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="AM19" s="2">
+      <c r="AM19" s="8">
         <v>5</v>
       </c>
       <c r="AN19" s="2" t="s">
@@ -11278,6 +11358,10 @@
       <c r="F20" s="3" t="s">
         <v>1902</v>
       </c>
+      <c r="G20" s="8"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
       <c r="K20" s="2" t="s">
         <v>76</v>
       </c>
@@ -11308,16 +11392,16 @@
       <c r="V20" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W20" s="2" t="s">
+      <c r="W20" s="8" t="s">
         <v>1897</v>
       </c>
       <c r="X20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y20" s="2" t="s">
+      <c r="Y20" s="8" t="s">
         <v>685</v>
       </c>
-      <c r="Z20" s="2" t="s">
+      <c r="Z20" s="8" t="s">
         <v>684</v>
       </c>
       <c r="AA20" s="4" t="s">
@@ -11335,10 +11419,10 @@
       <c r="AE20" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF20" s="4" t="s">
+      <c r="AF20" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="AG20" s="4" t="s">
+      <c r="AG20" s="13" t="s">
         <v>1080</v>
       </c>
       <c r="AH20" s="2" t="s">
@@ -11356,7 +11440,7 @@
       <c r="AL20" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="AM20" s="2">
+      <c r="AM20" s="8">
         <v>5</v>
       </c>
       <c r="AN20" s="2" t="s">
@@ -11394,6 +11478,10 @@
       <c r="F21" s="3" t="s">
         <v>1884</v>
       </c>
+      <c r="G21" s="8"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
       <c r="K21" s="2" t="s">
         <v>76</v>
       </c>
@@ -11424,16 +11512,16 @@
       <c r="V21" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="W21" s="2" t="s">
+      <c r="W21" s="8" t="s">
         <v>1880</v>
       </c>
       <c r="X21" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y21" s="2" t="s">
+      <c r="Y21" s="8" t="s">
         <v>1879</v>
       </c>
-      <c r="Z21" s="2" t="s">
+      <c r="Z21" s="8" t="s">
         <v>279</v>
       </c>
       <c r="AA21" s="4" t="s">
@@ -11451,10 +11539,10 @@
       <c r="AE21" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AF21" s="4" t="s">
+      <c r="AF21" s="13" t="s">
         <v>1877</v>
       </c>
-      <c r="AG21" s="4" t="s">
+      <c r="AG21" s="13" t="s">
         <v>160</v>
       </c>
       <c r="AH21" s="2" t="s">
@@ -11472,7 +11560,7 @@
       <c r="AL21" s="2" t="s">
         <v>1873</v>
       </c>
-      <c r="AM21" s="2" t="s">
+      <c r="AM21" s="8" t="s">
         <v>508</v>
       </c>
       <c r="AN21" s="2" t="s">
@@ -11510,6 +11598,10 @@
       <c r="F22" s="3" t="s">
         <v>1863</v>
       </c>
+      <c r="G22" s="8"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
       <c r="K22" s="2" t="s">
         <v>1862</v>
       </c>
@@ -11540,16 +11632,16 @@
       <c r="V22" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="W22" s="2" t="s">
+      <c r="W22" s="8" t="s">
         <v>1372</v>
       </c>
       <c r="X22" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y22" s="2" t="s">
+      <c r="Y22" s="8" t="s">
         <v>1857</v>
       </c>
-      <c r="Z22" s="2" t="s">
+      <c r="Z22" s="8" t="s">
         <v>889</v>
       </c>
       <c r="AA22" s="4" t="s">
@@ -11567,10 +11659,10 @@
       <c r="AE22" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF22" s="4" t="s">
+      <c r="AF22" s="13" t="s">
         <v>589</v>
       </c>
-      <c r="AG22" s="4" t="s">
+      <c r="AG22" s="13" t="s">
         <v>561</v>
       </c>
       <c r="AH22" s="2" t="s">
@@ -11588,7 +11680,7 @@
       <c r="AL22" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="AM22" s="2" t="s">
+      <c r="AM22" s="8" t="s">
         <v>241</v>
       </c>
       <c r="AN22" s="2" t="s">
@@ -11626,6 +11718,10 @@
       <c r="F23" s="3" t="s">
         <v>1844</v>
       </c>
+      <c r="G23" s="8"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
       <c r="K23" s="2" t="s">
         <v>1843</v>
       </c>
@@ -11656,16 +11752,16 @@
       <c r="V23" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W23" s="2" t="s">
+      <c r="W23" s="8" t="s">
         <v>413</v>
       </c>
       <c r="X23" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y23" s="2" t="s">
+      <c r="Y23" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="Z23" s="2" t="s">
+      <c r="Z23" s="8" t="s">
         <v>411</v>
       </c>
       <c r="AA23" s="4" t="s">
@@ -11683,10 +11779,10 @@
       <c r="AE23" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF23" s="4" t="s">
+      <c r="AF23" s="13" t="s">
         <v>486</v>
       </c>
-      <c r="AG23" s="4" t="s">
+      <c r="AG23" s="13" t="s">
         <v>1140</v>
       </c>
       <c r="AH23" s="2" t="s">
@@ -11704,7 +11800,7 @@
       <c r="AL23" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="AM23" s="2" t="s">
+      <c r="AM23" s="8" t="s">
         <v>787</v>
       </c>
       <c r="AN23" s="2" t="s">
@@ -11742,6 +11838,10 @@
       <c r="F24" s="3" t="s">
         <v>1827</v>
       </c>
+      <c r="G24" s="8"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
       <c r="K24" s="2" t="s">
         <v>1826</v>
       </c>
@@ -11772,16 +11872,16 @@
       <c r="V24" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="W24" s="2" t="s">
+      <c r="W24" s="8" t="s">
         <v>567</v>
       </c>
       <c r="X24" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y24" s="2" t="s">
+      <c r="Y24" s="8" t="s">
         <v>1821</v>
       </c>
-      <c r="Z24" s="2" t="s">
+      <c r="Z24" s="8" t="s">
         <v>565</v>
       </c>
       <c r="AA24" s="4" t="s">
@@ -11799,10 +11899,10 @@
       <c r="AE24" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AF24" s="4" t="s">
+      <c r="AF24" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="AG24" s="4" t="s">
+      <c r="AG24" s="13" t="s">
         <v>1819</v>
       </c>
       <c r="AH24" s="2" t="s">
@@ -11820,7 +11920,7 @@
       <c r="AL24" s="2" t="s">
         <v>1817</v>
       </c>
-      <c r="AM24" s="2" t="s">
+      <c r="AM24" s="8" t="s">
         <v>1816</v>
       </c>
       <c r="AN24" s="2" t="s">
@@ -11858,6 +11958,10 @@
       <c r="F25" s="3" t="s">
         <v>1806</v>
       </c>
+      <c r="G25" s="8"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
       <c r="K25" s="2" t="s">
         <v>667</v>
       </c>
@@ -11888,16 +11992,16 @@
       <c r="V25" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W25" s="2" t="s">
+      <c r="W25" s="8" t="s">
         <v>1584</v>
       </c>
       <c r="X25" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y25" s="2" t="s">
+      <c r="Y25" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="Z25" s="2" t="s">
+      <c r="Z25" s="8" t="s">
         <v>195</v>
       </c>
       <c r="AA25" s="4" t="s">
@@ -11915,10 +12019,10 @@
       <c r="AE25" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF25" s="4" t="s">
+      <c r="AF25" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="AG25" s="4" t="s">
+      <c r="AG25" s="13" t="s">
         <v>351</v>
       </c>
       <c r="AH25" s="2" t="s">
@@ -11936,7 +12040,7 @@
       <c r="AL25" s="2" t="s">
         <v>1801</v>
       </c>
-      <c r="AM25" s="2">
+      <c r="AM25" s="8">
         <v>3</v>
       </c>
       <c r="AN25" s="2" t="s">
@@ -11974,6 +12078,10 @@
       <c r="F26" s="3" t="s">
         <v>1792</v>
       </c>
+      <c r="G26" s="8"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
       <c r="K26" s="2" t="s">
         <v>1791</v>
       </c>
@@ -12004,16 +12112,16 @@
       <c r="V26" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W26" s="2" t="s">
+      <c r="W26" s="8" t="s">
         <v>413</v>
       </c>
       <c r="X26" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="Y26" s="2" t="s">
+      <c r="Y26" s="8" t="s">
         <v>731</v>
       </c>
-      <c r="Z26" s="2" t="s">
+      <c r="Z26" s="8" t="s">
         <v>730</v>
       </c>
       <c r="AA26" s="4" t="s">
@@ -12031,10 +12139,10 @@
       <c r="AE26" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF26" s="4" t="s">
+      <c r="AF26" s="13" t="s">
         <v>791</v>
       </c>
-      <c r="AG26" s="4" t="s">
+      <c r="AG26" s="13" t="s">
         <v>190</v>
       </c>
       <c r="AH26" s="2">
@@ -12052,7 +12160,7 @@
       <c r="AL26" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="AM26" s="2">
+      <c r="AM26" s="8">
         <v>3</v>
       </c>
       <c r="AN26" s="2" t="s">
@@ -12090,6 +12198,10 @@
       <c r="F27" s="3" t="s">
         <v>1773</v>
       </c>
+      <c r="G27" s="8"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
       <c r="K27" s="2" t="s">
         <v>76</v>
       </c>
@@ -12120,16 +12232,16 @@
       <c r="V27" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="W27" s="2" t="s">
+      <c r="W27" s="8" t="s">
         <v>308</v>
       </c>
       <c r="X27" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y27" s="2" t="s">
+      <c r="Y27" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="Z27" s="2" t="s">
+      <c r="Z27" s="8" t="s">
         <v>99</v>
       </c>
       <c r="AA27" s="4" t="s">
@@ -12147,10 +12259,10 @@
       <c r="AE27" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AF27" s="4" t="s">
+      <c r="AF27" s="13" t="s">
         <v>706</v>
       </c>
-      <c r="AG27" s="4" t="s">
+      <c r="AG27" s="13" t="s">
         <v>1140</v>
       </c>
       <c r="AH27" s="2" t="s">
@@ -12168,7 +12280,7 @@
       <c r="AL27" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="AM27" s="2">
+      <c r="AM27" s="8">
         <v>3</v>
       </c>
       <c r="AN27" s="2" t="s">
@@ -12206,6 +12318,10 @@
       <c r="F28" s="3" t="s">
         <v>1755</v>
       </c>
+      <c r="G28" s="8"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
       <c r="K28" s="2" t="s">
         <v>1754</v>
       </c>
@@ -12236,16 +12352,16 @@
       <c r="V28" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="W28" s="2" t="s">
+      <c r="W28" s="8" t="s">
         <v>1748</v>
       </c>
       <c r="X28" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y28" s="2" t="s">
+      <c r="Y28" s="8" t="s">
         <v>1747</v>
       </c>
-      <c r="Z28" s="2" t="s">
+      <c r="Z28" s="8" t="s">
         <v>1746</v>
       </c>
       <c r="AA28" s="4" t="s">
@@ -12263,10 +12379,10 @@
       <c r="AE28" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AF28" s="4" t="s">
+      <c r="AF28" s="13" t="s">
         <v>590</v>
       </c>
-      <c r="AG28" s="4" t="s">
+      <c r="AG28" s="13" t="s">
         <v>1517</v>
       </c>
       <c r="AH28" s="2" t="s">
@@ -12284,7 +12400,7 @@
       <c r="AL28" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="AM28" s="2" t="s">
+      <c r="AM28" s="8" t="s">
         <v>271</v>
       </c>
       <c r="AN28" s="2" t="s">
@@ -12322,6 +12438,10 @@
       <c r="F29" s="3" t="s">
         <v>1732</v>
       </c>
+      <c r="G29" s="8"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
       <c r="K29" s="2" t="s">
         <v>1731</v>
       </c>
@@ -12352,16 +12472,16 @@
       <c r="V29" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="W29" s="2" t="s">
+      <c r="W29" s="8" t="s">
         <v>1269</v>
       </c>
       <c r="X29" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y29" s="2" t="s">
+      <c r="Y29" s="8" t="s">
         <v>1268</v>
       </c>
-      <c r="Z29" s="2" t="s">
+      <c r="Z29" s="8" t="s">
         <v>411</v>
       </c>
       <c r="AA29" s="4" t="s">
@@ -12379,10 +12499,10 @@
       <c r="AE29" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AF29" s="4" t="s">
+      <c r="AF29" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="AG29" s="4" t="s">
+      <c r="AG29" s="13" t="s">
         <v>57</v>
       </c>
       <c r="AH29" s="2" t="s">
@@ -12400,7 +12520,7 @@
       <c r="AL29" s="2" t="s">
         <v>1725</v>
       </c>
-      <c r="AM29" s="2" t="s">
+      <c r="AM29" s="8" t="s">
         <v>309</v>
       </c>
       <c r="AN29" s="2" t="s">
@@ -12438,6 +12558,10 @@
       <c r="F30" s="3" t="s">
         <v>1715</v>
       </c>
+      <c r="G30" s="8"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
       <c r="K30" s="2" t="s">
         <v>1714</v>
       </c>
@@ -12468,16 +12592,16 @@
       <c r="V30" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="W30" s="2" t="s">
+      <c r="W30" s="8" t="s">
         <v>1541</v>
       </c>
       <c r="X30" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y30" s="2" t="s">
+      <c r="Y30" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="Z30" s="2" t="s">
+      <c r="Z30" s="8" t="s">
         <v>438</v>
       </c>
       <c r="AA30" s="4" t="s">
@@ -12495,10 +12619,10 @@
       <c r="AE30" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="AF30" s="4" t="s">
+      <c r="AF30" s="13" t="s">
         <v>1708</v>
       </c>
-      <c r="AG30" s="4" t="s">
+      <c r="AG30" s="13" t="s">
         <v>1101</v>
       </c>
       <c r="AH30" s="2" t="s">
@@ -12516,7 +12640,7 @@
       <c r="AL30" s="2" t="s">
         <v>1638</v>
       </c>
-      <c r="AM30" s="2" t="s">
+      <c r="AM30" s="8" t="s">
         <v>102</v>
       </c>
       <c r="AN30" s="2" t="s">
@@ -12554,6 +12678,10 @@
       <c r="F31" s="3" t="s">
         <v>1697</v>
       </c>
+      <c r="G31" s="8"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
       <c r="K31" s="2" t="s">
         <v>1696</v>
       </c>
@@ -12584,16 +12712,16 @@
       <c r="V31" s="2" t="s">
         <v>1308</v>
       </c>
-      <c r="W31" s="2" t="s">
+      <c r="W31" s="8" t="s">
         <v>1691</v>
       </c>
       <c r="X31" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="Y31" s="2" t="s">
+      <c r="Y31" s="8" t="s">
         <v>1690</v>
       </c>
-      <c r="Z31" s="2" t="s">
+      <c r="Z31" s="8" t="s">
         <v>933</v>
       </c>
       <c r="AA31" s="4" t="s">
@@ -12611,10 +12739,10 @@
       <c r="AE31" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AF31" s="4" t="s">
+      <c r="AF31" s="13" t="s">
         <v>1686</v>
       </c>
-      <c r="AG31" s="4" t="s">
+      <c r="AG31" s="13" t="s">
         <v>486</v>
       </c>
       <c r="AH31" s="2" t="s">
@@ -12632,7 +12760,7 @@
       <c r="AL31" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="AM31" s="2">
+      <c r="AM31" s="8">
         <v>6</v>
       </c>
       <c r="AN31" s="2" t="s">
@@ -12670,6 +12798,10 @@
       <c r="F32" s="3" t="s">
         <v>1674</v>
       </c>
+      <c r="G32" s="8"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
       <c r="K32" s="2" t="s">
         <v>76</v>
       </c>
@@ -12700,16 +12832,16 @@
       <c r="V32" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="W32" s="2" t="s">
+      <c r="W32" s="8" t="s">
         <v>1668</v>
       </c>
       <c r="X32" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y32" s="2" t="s">
+      <c r="Y32" s="8" t="s">
         <v>1667</v>
       </c>
-      <c r="Z32" s="2" t="s">
+      <c r="Z32" s="8" t="s">
         <v>1666</v>
       </c>
       <c r="AA32" s="4" t="s">
@@ -12727,10 +12859,10 @@
       <c r="AE32" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="AF32" s="4" t="s">
+      <c r="AF32" s="13" t="s">
         <v>1311</v>
       </c>
-      <c r="AG32" s="4" t="s">
+      <c r="AG32" s="13" t="s">
         <v>1663</v>
       </c>
       <c r="AH32" s="2" t="s">
@@ -12748,7 +12880,7 @@
       <c r="AL32" s="2" t="s">
         <v>1638</v>
       </c>
-      <c r="AM32" s="2" t="s">
+      <c r="AM32" s="8" t="s">
         <v>634</v>
       </c>
       <c r="AN32" s="2" t="s">
@@ -12786,6 +12918,10 @@
       <c r="F33" s="3" t="s">
         <v>1651</v>
       </c>
+      <c r="G33" s="8"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
       <c r="K33" s="2" t="s">
         <v>1650</v>
       </c>
@@ -12816,16 +12952,16 @@
       <c r="V33" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="W33" s="2" t="s">
+      <c r="W33" s="8" t="s">
         <v>1644</v>
       </c>
       <c r="X33" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y33" s="2" t="s">
+      <c r="Y33" s="8" t="s">
         <v>1643</v>
       </c>
-      <c r="Z33" s="2" t="s">
+      <c r="Z33" s="8" t="s">
         <v>438</v>
       </c>
       <c r="AA33" s="4" t="s">
@@ -12843,10 +12979,10 @@
       <c r="AE33" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AF33" s="4" t="s">
+      <c r="AF33" s="13" t="s">
         <v>1641</v>
       </c>
-      <c r="AG33" s="4" t="s">
+      <c r="AG33" s="13" t="s">
         <v>1640</v>
       </c>
       <c r="AH33" s="2" t="s">
@@ -12864,7 +13000,7 @@
       <c r="AL33" s="2" t="s">
         <v>1638</v>
       </c>
-      <c r="AM33" s="2" t="s">
+      <c r="AM33" s="8" t="s">
         <v>241</v>
       </c>
       <c r="AN33" s="2" t="s">
@@ -12902,6 +13038,10 @@
       <c r="F34" s="3" t="s">
         <v>1628</v>
       </c>
+      <c r="G34" s="8"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
       <c r="K34" s="2" t="s">
         <v>76</v>
       </c>
@@ -12932,16 +13072,16 @@
       <c r="V34" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="W34" s="2" t="s">
+      <c r="W34" s="8" t="s">
         <v>331</v>
       </c>
       <c r="X34" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y34" s="2" t="s">
+      <c r="Y34" s="8" t="s">
         <v>1623</v>
       </c>
-      <c r="Z34" s="2" t="s">
+      <c r="Z34" s="8" t="s">
         <v>1622</v>
       </c>
       <c r="AA34" s="4" t="s">
@@ -12959,10 +13099,10 @@
       <c r="AE34" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF34" s="4" t="s">
+      <c r="AF34" s="13" t="s">
         <v>706</v>
       </c>
-      <c r="AG34" s="4" t="s">
+      <c r="AG34" s="13" t="s">
         <v>791</v>
       </c>
       <c r="AH34" s="2" t="s">
@@ -12980,7 +13120,7 @@
       <c r="AL34" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="AM34" s="2" t="s">
+      <c r="AM34" s="8" t="s">
         <v>241</v>
       </c>
       <c r="AN34" s="2" t="s">
@@ -13018,6 +13158,10 @@
       <c r="F35" s="3" t="s">
         <v>1609</v>
       </c>
+      <c r="G35" s="8"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
       <c r="K35" s="2" t="s">
         <v>1608</v>
       </c>
@@ -13048,16 +13192,16 @@
       <c r="V35" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W35" s="2" t="s">
+      <c r="W35" s="8" t="s">
         <v>1603</v>
       </c>
       <c r="X35" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y35" s="2" t="s">
+      <c r="Y35" s="8" t="s">
         <v>731</v>
       </c>
-      <c r="Z35" s="2" t="s">
+      <c r="Z35" s="8" t="s">
         <v>889</v>
       </c>
       <c r="AA35" s="4" t="s">
@@ -13075,10 +13219,10 @@
       <c r="AE35" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF35" s="4" t="s">
+      <c r="AF35" s="13" t="s">
         <v>561</v>
       </c>
-      <c r="AG35" s="4" t="s">
+      <c r="AG35" s="13" t="s">
         <v>1080</v>
       </c>
       <c r="AH35" s="2" t="s">
@@ -13096,7 +13240,7 @@
       <c r="AL35" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AM35" s="2" t="s">
+      <c r="AM35" s="8" t="s">
         <v>243</v>
       </c>
       <c r="AN35" s="2" t="s">
@@ -13134,6 +13278,10 @@
       <c r="F36" s="3" t="s">
         <v>1590</v>
       </c>
+      <c r="G36" s="8"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
       <c r="K36" s="2" t="s">
         <v>1589</v>
       </c>
@@ -13164,16 +13312,16 @@
       <c r="V36" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="W36" s="2" t="s">
+      <c r="W36" s="8" t="s">
         <v>1584</v>
       </c>
       <c r="X36" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y36" s="2" t="s">
+      <c r="Y36" s="8" t="s">
         <v>731</v>
       </c>
-      <c r="Z36" s="2" t="s">
+      <c r="Z36" s="8" t="s">
         <v>730</v>
       </c>
       <c r="AA36" s="4" t="s">
@@ -13191,10 +13339,10 @@
       <c r="AE36" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AF36" s="4" t="s">
+      <c r="AF36" s="13" t="s">
         <v>1582</v>
       </c>
-      <c r="AG36" s="4" t="s">
+      <c r="AG36" s="13" t="s">
         <v>1581</v>
       </c>
       <c r="AH36" s="2" t="s">
@@ -13212,7 +13360,7 @@
       <c r="AL36" s="2" t="s">
         <v>1580</v>
       </c>
-      <c r="AM36" s="2" t="s">
+      <c r="AM36" s="8" t="s">
         <v>642</v>
       </c>
       <c r="AN36" s="2" t="s">
@@ -13250,6 +13398,10 @@
       <c r="F37" s="3" t="s">
         <v>1569</v>
       </c>
+      <c r="G37" s="8"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
       <c r="K37" s="2" t="s">
         <v>1568</v>
       </c>
@@ -13280,16 +13432,16 @@
       <c r="V37" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="W37" s="2" t="s">
+      <c r="W37" s="8" t="s">
         <v>1563</v>
       </c>
       <c r="X37" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="Y37" s="2" t="s">
+      <c r="Y37" s="8" t="s">
         <v>1562</v>
       </c>
-      <c r="Z37" s="2" t="s">
+      <c r="Z37" s="8" t="s">
         <v>1561</v>
       </c>
       <c r="AA37" s="4" t="s">
@@ -13307,10 +13459,10 @@
       <c r="AE37" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AF37" s="4" t="s">
+      <c r="AF37" s="13" t="s">
         <v>562</v>
       </c>
-      <c r="AG37" s="4" t="s">
+      <c r="AG37" s="13" t="s">
         <v>561</v>
       </c>
       <c r="AH37" s="2" t="s">
@@ -13328,7 +13480,7 @@
       <c r="AL37" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="AM37" s="2">
+      <c r="AM37" s="8">
         <v>8</v>
       </c>
       <c r="AN37" s="2" t="s">
@@ -13366,6 +13518,10 @@
       <c r="F38" s="3" t="s">
         <v>1547</v>
       </c>
+      <c r="G38" s="8"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
       <c r="K38" s="2" t="s">
         <v>76</v>
       </c>
@@ -13396,16 +13552,16 @@
       <c r="V38" s="2" t="s">
         <v>1542</v>
       </c>
-      <c r="W38" s="2" t="s">
+      <c r="W38" s="8" t="s">
         <v>1541</v>
       </c>
       <c r="X38" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y38" s="2" t="s">
+      <c r="Y38" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="Z38" s="2" t="s">
+      <c r="Z38" s="8" t="s">
         <v>438</v>
       </c>
       <c r="AA38" s="4" t="s">
@@ -13423,10 +13579,10 @@
       <c r="AE38" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AF38" s="4" t="s">
+      <c r="AF38" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="AG38" s="4" t="s">
+      <c r="AG38" s="13" t="s">
         <v>929</v>
       </c>
       <c r="AH38" s="2" t="s">
@@ -13444,7 +13600,7 @@
       <c r="AL38" s="2" t="s">
         <v>1536</v>
       </c>
-      <c r="AM38" s="2" t="s">
+      <c r="AM38" s="8" t="s">
         <v>585</v>
       </c>
       <c r="AN38" s="2" t="s">
@@ -13482,6 +13638,10 @@
       <c r="F39" s="3" t="s">
         <v>1526</v>
       </c>
+      <c r="G39" s="8"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
       <c r="K39" s="2" t="s">
         <v>76</v>
       </c>
@@ -13512,16 +13672,16 @@
       <c r="V39" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="W39" s="2" t="s">
+      <c r="W39" s="8" t="s">
         <v>308</v>
       </c>
       <c r="X39" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="Y39" s="2" t="s">
+      <c r="Y39" s="8" t="s">
         <v>1520</v>
       </c>
-      <c r="Z39" s="2" t="s">
+      <c r="Z39" s="8" t="s">
         <v>99</v>
       </c>
       <c r="AA39" s="4" t="s">
@@ -13539,10 +13699,10 @@
       <c r="AE39" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AF39" s="4" t="s">
+      <c r="AF39" s="13" t="s">
         <v>1518</v>
       </c>
-      <c r="AG39" s="4" t="s">
+      <c r="AG39" s="13" t="s">
         <v>1517</v>
       </c>
       <c r="AH39" s="2" t="s">
@@ -13560,7 +13720,7 @@
       <c r="AL39" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="AM39" s="2" t="s">
+      <c r="AM39" s="8" t="s">
         <v>535</v>
       </c>
       <c r="AN39" s="2" t="s">
@@ -13598,6 +13758,10 @@
       <c r="F40" s="3" t="s">
         <v>1505</v>
       </c>
+      <c r="G40" s="8"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
       <c r="K40" s="2" t="s">
         <v>1504</v>
       </c>
@@ -13628,16 +13792,16 @@
       <c r="V40" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="W40" s="2" t="s">
+      <c r="W40" s="8" t="s">
         <v>1499</v>
       </c>
       <c r="X40" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y40" s="2" t="s">
+      <c r="Y40" s="8" t="s">
         <v>1498</v>
       </c>
-      <c r="Z40" s="2" t="s">
+      <c r="Z40" s="8" t="s">
         <v>1497</v>
       </c>
       <c r="AA40" s="4" t="s">
@@ -13655,10 +13819,10 @@
       <c r="AE40" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AF40" s="4" t="s">
+      <c r="AF40" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="AG40" s="4" t="s">
+      <c r="AG40" s="13" t="s">
         <v>57</v>
       </c>
       <c r="AH40" s="2" t="s">
@@ -13676,7 +13840,7 @@
       <c r="AL40" s="2" t="s">
         <v>1491</v>
       </c>
-      <c r="AM40" s="2" t="s">
+      <c r="AM40" s="8" t="s">
         <v>157</v>
       </c>
       <c r="AN40" s="2" t="s">
@@ -13714,6 +13878,10 @@
       <c r="F41" s="3" t="s">
         <v>1480</v>
       </c>
+      <c r="G41" s="8"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
       <c r="K41" s="2" t="s">
         <v>1479</v>
       </c>
@@ -13744,16 +13912,16 @@
       <c r="V41" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="W41" s="2" t="s">
+      <c r="W41" s="8" t="s">
         <v>1473</v>
       </c>
       <c r="X41" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="Y41" s="2" t="s">
+      <c r="Y41" s="8" t="s">
         <v>911</v>
       </c>
-      <c r="Z41" s="2" t="s">
+      <c r="Z41" s="8" t="s">
         <v>1472</v>
       </c>
       <c r="AA41" s="4" t="s">
@@ -13771,10 +13939,10 @@
       <c r="AE41" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AF41" s="4" t="s">
+      <c r="AF41" s="13" t="s">
         <v>408</v>
       </c>
-      <c r="AG41" s="4" t="s">
+      <c r="AG41" s="13" t="s">
         <v>733</v>
       </c>
       <c r="AH41" s="2" t="s">
@@ -13792,7 +13960,7 @@
       <c r="AL41" s="2" t="s">
         <v>1467</v>
       </c>
-      <c r="AM41" s="2" t="s">
+      <c r="AM41" s="8" t="s">
         <v>1466</v>
       </c>
       <c r="AN41" s="2" t="s">
@@ -13830,6 +13998,10 @@
       <c r="F42" s="3" t="s">
         <v>1455</v>
       </c>
+      <c r="G42" s="8"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="11"/>
       <c r="K42" s="2" t="s">
         <v>1454</v>
       </c>
@@ -13860,16 +14032,16 @@
       <c r="V42" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W42" s="2" t="s">
+      <c r="W42" s="8" t="s">
         <v>1082</v>
       </c>
       <c r="X42" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y42" s="2" t="s">
+      <c r="Y42" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="Z42" s="2" t="s">
+      <c r="Z42" s="8" t="s">
         <v>221</v>
       </c>
       <c r="AA42" s="4" t="s">
@@ -13887,10 +14059,10 @@
       <c r="AE42" s="4" t="s">
         <v>1447</v>
       </c>
-      <c r="AF42" s="4" t="s">
+      <c r="AF42" s="13" t="s">
         <v>1446</v>
       </c>
-      <c r="AG42" s="4" t="s">
+      <c r="AG42" s="13" t="s">
         <v>1445</v>
       </c>
       <c r="AH42" s="2" t="s">
@@ -13908,7 +14080,7 @@
       <c r="AL42" s="2" t="s">
         <v>1442</v>
       </c>
-      <c r="AM42" s="2">
+      <c r="AM42" s="8">
         <v>45659</v>
       </c>
       <c r="AN42" s="2" t="s">
@@ -13946,6 +14118,10 @@
       <c r="F43" s="3" t="s">
         <v>1431</v>
       </c>
+      <c r="G43" s="8"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
       <c r="K43" s="2" t="s">
         <v>1430</v>
       </c>
@@ -13976,16 +14152,16 @@
       <c r="V43" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W43" s="2" t="s">
+      <c r="W43" s="8" t="s">
         <v>413</v>
       </c>
       <c r="X43" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y43" s="2" t="s">
+      <c r="Y43" s="8" t="s">
         <v>1247</v>
       </c>
-      <c r="Z43" s="2" t="s">
+      <c r="Z43" s="8" t="s">
         <v>1424</v>
       </c>
       <c r="AA43" s="4" t="s">
@@ -14003,10 +14179,10 @@
       <c r="AE43" s="4" t="s">
         <v>638</v>
       </c>
-      <c r="AF43" s="4" t="s">
+      <c r="AF43" s="13" t="s">
         <v>637</v>
       </c>
-      <c r="AG43" s="4" t="s">
+      <c r="AG43" s="13" t="s">
         <v>814</v>
       </c>
       <c r="AH43" s="2" t="s">
@@ -14024,7 +14200,7 @@
       <c r="AL43" s="2" t="s">
         <v>1420</v>
       </c>
-      <c r="AM43" s="2" t="s">
+      <c r="AM43" s="8" t="s">
         <v>678</v>
       </c>
       <c r="AN43" s="2" t="s">
@@ -14062,6 +14238,10 @@
       <c r="F44" s="3" t="s">
         <v>1409</v>
       </c>
+      <c r="G44" s="8"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
       <c r="K44" s="2" t="s">
         <v>1408</v>
       </c>
@@ -14092,16 +14272,16 @@
       <c r="V44" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W44" s="2" t="s">
+      <c r="W44" s="8" t="s">
         <v>862</v>
       </c>
       <c r="X44" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="Y44" s="2" t="s">
+      <c r="Y44" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="Z44" s="2" t="s">
+      <c r="Z44" s="8" t="s">
         <v>794</v>
       </c>
       <c r="AA44" s="4" t="s">
@@ -14119,10 +14299,10 @@
       <c r="AE44" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF44" s="4" t="s">
+      <c r="AF44" s="13" t="s">
         <v>486</v>
       </c>
-      <c r="AG44" s="4" t="s">
+      <c r="AG44" s="13" t="s">
         <v>791</v>
       </c>
       <c r="AH44" s="2" t="s">
@@ -14140,7 +14320,7 @@
       <c r="AL44" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="AM44" s="2" t="s">
+      <c r="AM44" s="8" t="s">
         <v>678</v>
       </c>
       <c r="AN44" s="2" t="s">
@@ -14178,6 +14358,10 @@
       <c r="F45" s="3" t="s">
         <v>1393</v>
       </c>
+      <c r="G45" s="8"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
       <c r="K45" s="2" t="s">
         <v>1392</v>
       </c>
@@ -14208,16 +14392,16 @@
       <c r="V45" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W45" s="2" t="s">
+      <c r="W45" s="8" t="s">
         <v>617</v>
       </c>
       <c r="X45" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y45" s="2" t="s">
+      <c r="Y45" s="8" t="s">
         <v>1021</v>
       </c>
-      <c r="Z45" s="2" t="s">
+      <c r="Z45" s="8" t="s">
         <v>1020</v>
       </c>
       <c r="AA45" s="4" t="s">
@@ -14235,10 +14419,10 @@
       <c r="AE45" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF45" s="4" t="s">
+      <c r="AF45" s="13" t="s">
         <v>791</v>
       </c>
-      <c r="AG45" s="4" t="s">
+      <c r="AG45" s="13" t="s">
         <v>790</v>
       </c>
       <c r="AH45" s="2" t="s">
@@ -14256,7 +14440,7 @@
       <c r="AL45" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="AM45" s="2">
+      <c r="AM45" s="8">
         <v>3</v>
       </c>
       <c r="AN45" s="2" t="s">
@@ -14294,6 +14478,10 @@
       <c r="F46" s="3" t="s">
         <v>1378</v>
       </c>
+      <c r="G46" s="8"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
       <c r="K46" s="2" t="s">
         <v>1377</v>
       </c>
@@ -14324,16 +14512,16 @@
       <c r="V46" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="W46" s="2" t="s">
+      <c r="W46" s="8" t="s">
         <v>1372</v>
       </c>
       <c r="X46" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y46" s="2" t="s">
+      <c r="Y46" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="Z46" s="2" t="s">
+      <c r="Z46" s="8" t="s">
         <v>357</v>
       </c>
       <c r="AA46" s="4" t="s">
@@ -14351,10 +14539,10 @@
       <c r="AE46" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF46" s="4" t="s">
+      <c r="AF46" s="13" t="s">
         <v>706</v>
       </c>
-      <c r="AG46" s="4" t="s">
+      <c r="AG46" s="13" t="s">
         <v>191</v>
       </c>
       <c r="AH46" s="2" t="s">
@@ -14372,7 +14560,7 @@
       <c r="AL46" s="2" t="s">
         <v>1369</v>
       </c>
-      <c r="AM46" s="2" t="s">
+      <c r="AM46" s="8" t="s">
         <v>241</v>
       </c>
       <c r="AN46" s="2" t="s">
@@ -14410,6 +14598,10 @@
       <c r="F47" s="3" t="s">
         <v>1359</v>
       </c>
+      <c r="G47" s="8"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="11"/>
       <c r="K47" s="2" t="s">
         <v>1358</v>
       </c>
@@ -14440,16 +14632,16 @@
       <c r="V47" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W47" s="2" t="s">
+      <c r="W47" s="8" t="s">
         <v>386</v>
       </c>
       <c r="X47" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y47" s="2" t="s">
+      <c r="Y47" s="8" t="s">
         <v>616</v>
       </c>
-      <c r="Z47" s="2" t="s">
+      <c r="Z47" s="8" t="s">
         <v>615</v>
       </c>
       <c r="AA47" s="4" t="s">
@@ -14467,10 +14659,10 @@
       <c r="AE47" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF47" s="4" t="s">
+      <c r="AF47" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="AG47" s="4" t="s">
+      <c r="AG47" s="13" t="s">
         <v>791</v>
       </c>
       <c r="AH47" s="2" t="s">
@@ -14488,7 +14680,7 @@
       <c r="AL47" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="AM47" s="2" t="s">
+      <c r="AM47" s="8" t="s">
         <v>787</v>
       </c>
       <c r="AN47" s="2" t="s">
@@ -14526,6 +14718,10 @@
       <c r="F48" s="3" t="s">
         <v>1343</v>
       </c>
+      <c r="G48" s="8"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="11"/>
       <c r="K48" s="2" t="s">
         <v>76</v>
       </c>
@@ -14556,16 +14752,16 @@
       <c r="V48" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W48" s="2" t="s">
+      <c r="W48" s="8" t="s">
         <v>1339</v>
       </c>
       <c r="X48" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="Y48" s="2" t="s">
+      <c r="Y48" s="8" t="s">
         <v>1338</v>
       </c>
-      <c r="Z48" s="2" t="s">
+      <c r="Z48" s="8" t="s">
         <v>862</v>
       </c>
       <c r="AA48" s="4" t="s">
@@ -14583,10 +14779,10 @@
       <c r="AE48" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AF48" s="4" t="s">
+      <c r="AF48" s="13" t="s">
         <v>791</v>
       </c>
-      <c r="AG48" s="4" t="s">
+      <c r="AG48" s="13" t="s">
         <v>1335</v>
       </c>
       <c r="AH48" s="2" t="s">
@@ -14604,7 +14800,7 @@
       <c r="AL48" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="AM48" s="2">
+      <c r="AM48" s="8">
         <v>1</v>
       </c>
       <c r="AN48" s="2" t="s">
@@ -14642,6 +14838,10 @@
       <c r="F49" s="3" t="s">
         <v>1325</v>
       </c>
+      <c r="G49" s="8"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="11"/>
       <c r="K49" s="2" t="s">
         <v>1324</v>
       </c>
@@ -14672,16 +14872,16 @@
       <c r="V49" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="W49" s="2" t="s">
+      <c r="W49" s="8" t="s">
         <v>1318</v>
       </c>
       <c r="X49" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y49" s="2" t="s">
+      <c r="Y49" s="8" t="s">
         <v>1317</v>
       </c>
-      <c r="Z49" s="2" t="s">
+      <c r="Z49" s="8" t="s">
         <v>1316</v>
       </c>
       <c r="AA49" s="4" t="s">
@@ -14699,10 +14899,10 @@
       <c r="AE49" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="AF49" s="4" t="s">
+      <c r="AF49" s="13" t="s">
         <v>1312</v>
       </c>
-      <c r="AG49" s="4" t="s">
+      <c r="AG49" s="13" t="s">
         <v>1311</v>
       </c>
       <c r="AH49" s="2" t="s">
@@ -14720,7 +14920,7 @@
       <c r="AL49" s="2" t="s">
         <v>1307</v>
       </c>
-      <c r="AM49" s="2" t="s">
+      <c r="AM49" s="8" t="s">
         <v>1306</v>
       </c>
       <c r="AN49" s="2" t="s">
@@ -14758,6 +14958,10 @@
       <c r="F50" s="3" t="s">
         <v>1295</v>
       </c>
+      <c r="G50" s="8"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
+      <c r="J50" s="11"/>
       <c r="K50" s="2" t="s">
         <v>1294</v>
       </c>
@@ -14788,16 +14992,16 @@
       <c r="V50" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="W50" s="2" t="s">
+      <c r="W50" s="8" t="s">
         <v>440</v>
       </c>
       <c r="X50" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y50" s="2" t="s">
+      <c r="Y50" s="8" t="s">
         <v>593</v>
       </c>
-      <c r="Z50" s="2" t="s">
+      <c r="Z50" s="8" t="s">
         <v>279</v>
       </c>
       <c r="AA50" s="4" t="s">
@@ -14815,10 +15019,10 @@
       <c r="AE50" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AF50" s="4" t="s">
+      <c r="AF50" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="AG50" s="4" t="s">
+      <c r="AG50" s="13" t="s">
         <v>814</v>
       </c>
       <c r="AH50" s="2" t="s">
@@ -14836,7 +15040,7 @@
       <c r="AL50" s="2" t="s">
         <v>1285</v>
       </c>
-      <c r="AM50" s="2">
+      <c r="AM50" s="8">
         <v>7</v>
       </c>
       <c r="AN50" s="2" t="s">
@@ -14874,6 +15078,10 @@
       <c r="F51" s="3" t="s">
         <v>1275</v>
       </c>
+      <c r="G51" s="8"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="11"/>
       <c r="K51" s="2" t="s">
         <v>1274</v>
       </c>
@@ -14904,16 +15112,16 @@
       <c r="V51" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="W51" s="2" t="s">
+      <c r="W51" s="8" t="s">
         <v>1269</v>
       </c>
       <c r="X51" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y51" s="2" t="s">
+      <c r="Y51" s="8" t="s">
         <v>1268</v>
       </c>
-      <c r="Z51" s="2" t="s">
+      <c r="Z51" s="8" t="s">
         <v>385</v>
       </c>
       <c r="AA51" s="4" t="s">
@@ -14931,10 +15139,10 @@
       <c r="AE51" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF51" s="4" t="s">
+      <c r="AF51" s="13" t="s">
         <v>838</v>
       </c>
-      <c r="AG51" s="4" t="s">
+      <c r="AG51" s="13" t="s">
         <v>791</v>
       </c>
       <c r="AH51" s="2" t="s">
@@ -14952,7 +15160,7 @@
       <c r="AL51" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="AM51" s="2" t="s">
+      <c r="AM51" s="8" t="s">
         <v>585</v>
       </c>
       <c r="AN51" s="2" t="s">
@@ -14990,6 +15198,10 @@
       <c r="F52" s="3" t="s">
         <v>1255</v>
       </c>
+      <c r="G52" s="8"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="11"/>
+      <c r="J52" s="11"/>
       <c r="K52" s="2" t="s">
         <v>1254</v>
       </c>
@@ -15020,16 +15232,16 @@
       <c r="V52" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W52" s="2" t="s">
+      <c r="W52" s="8" t="s">
         <v>1248</v>
       </c>
       <c r="X52" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y52" s="2" t="s">
+      <c r="Y52" s="8" t="s">
         <v>1247</v>
       </c>
-      <c r="Z52" s="2" t="s">
+      <c r="Z52" s="8" t="s">
         <v>1246</v>
       </c>
       <c r="AA52" s="4" t="s">
@@ -15047,10 +15259,10 @@
       <c r="AE52" s="4" t="s">
         <v>638</v>
       </c>
-      <c r="AF52" s="4" t="s">
+      <c r="AF52" s="13" t="s">
         <v>408</v>
       </c>
-      <c r="AG52" s="4" t="s">
+      <c r="AG52" s="13" t="s">
         <v>733</v>
       </c>
       <c r="AH52" s="2" t="s">
@@ -15068,7 +15280,7 @@
       <c r="AL52" s="2" t="s">
         <v>1242</v>
       </c>
-      <c r="AM52" s="2" t="s">
+      <c r="AM52" s="8" t="s">
         <v>241</v>
       </c>
       <c r="AN52" s="2" t="s">
@@ -15106,6 +15318,10 @@
       <c r="F53" s="3" t="s">
         <v>1232</v>
       </c>
+      <c r="G53" s="8"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="11"/>
       <c r="K53" s="2" t="s">
         <v>1231</v>
       </c>
@@ -15136,16 +15352,16 @@
       <c r="V53" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W53" s="2" t="s">
+      <c r="W53" s="8" t="s">
         <v>617</v>
       </c>
       <c r="X53" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="Y53" s="2" t="s">
+      <c r="Y53" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="Z53" s="2" t="s">
+      <c r="Z53" s="8" t="s">
         <v>195</v>
       </c>
       <c r="AA53" s="4" t="s">
@@ -15163,10 +15379,10 @@
       <c r="AE53" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF53" s="4" t="s">
+      <c r="AF53" s="13" t="s">
         <v>538</v>
       </c>
-      <c r="AG53" s="4" t="s">
+      <c r="AG53" s="13" t="s">
         <v>561</v>
       </c>
       <c r="AH53" s="2" t="s">
@@ -15184,7 +15400,7 @@
       <c r="AL53" s="2" t="s">
         <v>1222</v>
       </c>
-      <c r="AM53" s="2" t="s">
+      <c r="AM53" s="8" t="s">
         <v>585</v>
       </c>
       <c r="AN53" s="2" t="s">
@@ -15222,6 +15438,10 @@
       <c r="F54" s="3" t="s">
         <v>1213</v>
       </c>
+      <c r="G54" s="8"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="11"/>
+      <c r="J54" s="11"/>
       <c r="K54" s="2" t="s">
         <v>1212</v>
       </c>
@@ -15252,16 +15472,16 @@
       <c r="V54" s="2">
         <v>67</v>
       </c>
-      <c r="W54" s="2" t="s">
+      <c r="W54" s="8" t="s">
         <v>1207</v>
       </c>
       <c r="X54" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y54" s="2" t="s">
+      <c r="Y54" s="8" t="s">
         <v>1167</v>
       </c>
-      <c r="Z54" s="2" t="s">
+      <c r="Z54" s="8" t="s">
         <v>889</v>
       </c>
       <c r="AA54" s="4" t="s">
@@ -15279,10 +15499,10 @@
       <c r="AE54" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AF54" s="9">
+      <c r="AF54" s="13">
         <v>130000</v>
       </c>
-      <c r="AG54" s="9">
+      <c r="AG54" s="13">
         <v>5000</v>
       </c>
       <c r="AH54" s="2" t="s">
@@ -15300,7 +15520,7 @@
       <c r="AL54" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="AM54" s="2">
+      <c r="AM54" s="8">
         <v>434</v>
       </c>
       <c r="AN54" s="2" t="s">
@@ -15338,6 +15558,10 @@
       <c r="F55" s="3" t="s">
         <v>1193</v>
       </c>
+      <c r="G55" s="8"/>
+      <c r="H55" s="11"/>
+      <c r="I55" s="11"/>
+      <c r="J55" s="11"/>
       <c r="K55" s="2" t="s">
         <v>76</v>
       </c>
@@ -15368,16 +15592,16 @@
       <c r="V55" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W55" s="2" t="s">
+      <c r="W55" s="8" t="s">
         <v>770</v>
       </c>
       <c r="X55" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y55" s="2" t="s">
+      <c r="Y55" s="8" t="s">
         <v>593</v>
       </c>
-      <c r="Z55" s="2" t="s">
+      <c r="Z55" s="8" t="s">
         <v>279</v>
       </c>
       <c r="AA55" s="4" t="s">
@@ -15395,10 +15619,10 @@
       <c r="AE55" s="4" t="s">
         <v>792</v>
       </c>
-      <c r="AF55" s="4" t="s">
+      <c r="AF55" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="AG55" s="4" t="s">
+      <c r="AG55" s="13" t="s">
         <v>1184</v>
       </c>
       <c r="AH55" s="2" t="s">
@@ -15416,7 +15640,7 @@
       <c r="AL55" s="2" t="s">
         <v>1182</v>
       </c>
-      <c r="AM55" s="2">
+      <c r="AM55" s="8">
         <v>1</v>
       </c>
       <c r="AN55" s="2" t="s">
@@ -15454,6 +15678,10 @@
       <c r="F56" s="3" t="s">
         <v>1172</v>
       </c>
+      <c r="G56" s="8"/>
+      <c r="H56" s="11"/>
+      <c r="I56" s="11"/>
+      <c r="J56" s="11"/>
       <c r="K56" s="2" t="s">
         <v>622</v>
       </c>
@@ -15484,16 +15712,16 @@
       <c r="V56" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="W56" s="2" t="s">
+      <c r="W56" s="8" t="s">
         <v>1167</v>
       </c>
       <c r="X56" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y56" s="2" t="s">
+      <c r="Y56" s="8" t="s">
         <v>1166</v>
       </c>
-      <c r="Z56" s="2" t="s">
+      <c r="Z56" s="8" t="s">
         <v>1165</v>
       </c>
       <c r="AA56" s="4" t="s">
@@ -15511,10 +15739,10 @@
       <c r="AE56" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AF56" s="4" t="s">
+      <c r="AF56" s="13" t="s">
         <v>1162</v>
       </c>
-      <c r="AG56" s="4" t="s">
+      <c r="AG56" s="13" t="s">
         <v>161</v>
       </c>
       <c r="AH56" s="2" t="s">
@@ -15532,7 +15760,7 @@
       <c r="AL56" s="2" t="s">
         <v>1159</v>
       </c>
-      <c r="AM56" s="2" t="s">
+      <c r="AM56" s="8" t="s">
         <v>1158</v>
       </c>
       <c r="AN56" s="2" t="s">
@@ -15570,6 +15798,10 @@
       <c r="F57" s="3" t="s">
         <v>1148</v>
       </c>
+      <c r="G57" s="8"/>
+      <c r="H57" s="11"/>
+      <c r="I57" s="11"/>
+      <c r="J57" s="11"/>
       <c r="K57" s="2" t="s">
         <v>1147</v>
       </c>
@@ -15600,16 +15832,16 @@
       <c r="V57" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="W57" s="2" t="s">
+      <c r="W57" s="8" t="s">
         <v>1142</v>
       </c>
       <c r="X57" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y57" s="2" t="s">
+      <c r="Y57" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="Z57" s="2" t="s">
+      <c r="Z57" s="8" t="s">
         <v>411</v>
       </c>
       <c r="AA57" s="4" t="s">
@@ -15627,10 +15859,10 @@
       <c r="AE57" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF57" s="4" t="s">
+      <c r="AF57" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="AG57" s="4" t="s">
+      <c r="AG57" s="13" t="s">
         <v>1140</v>
       </c>
       <c r="AH57" s="2" t="s">
@@ -15648,7 +15880,7 @@
       <c r="AL57" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="AM57" s="2" t="s">
+      <c r="AM57" s="8" t="s">
         <v>535</v>
       </c>
       <c r="AN57" s="2" t="s">
@@ -15686,6 +15918,10 @@
       <c r="F58" s="3" t="s">
         <v>1131</v>
       </c>
+      <c r="G58" s="8"/>
+      <c r="H58" s="11"/>
+      <c r="I58" s="11"/>
+      <c r="J58" s="11"/>
       <c r="K58" s="2" t="s">
         <v>76</v>
       </c>
@@ -15716,16 +15952,16 @@
       <c r="V58" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="W58" s="2" t="s">
+      <c r="W58" s="8" t="s">
         <v>686</v>
       </c>
       <c r="X58" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y58" s="2" t="s">
+      <c r="Y58" s="8" t="s">
         <v>1126</v>
       </c>
-      <c r="Z58" s="2" t="s">
+      <c r="Z58" s="8" t="s">
         <v>752</v>
       </c>
       <c r="AA58" s="4" t="s">
@@ -15743,10 +15979,10 @@
       <c r="AE58" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AF58" s="4" t="s">
+      <c r="AF58" s="13" t="s">
         <v>1123</v>
       </c>
-      <c r="AG58" s="4" t="s">
+      <c r="AG58" s="13" t="s">
         <v>408</v>
       </c>
       <c r="AH58" s="2" t="s">
@@ -15764,7 +16000,7 @@
       <c r="AL58" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AM58" s="2" t="s">
+      <c r="AM58" s="8" t="s">
         <v>1120</v>
       </c>
       <c r="AN58" s="2" t="s">
@@ -15802,6 +16038,10 @@
       <c r="F59" s="3" t="s">
         <v>1109</v>
       </c>
+      <c r="G59" s="8"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="11"/>
+      <c r="J59" s="11"/>
       <c r="K59" s="2" t="s">
         <v>1108</v>
       </c>
@@ -15832,16 +16072,16 @@
       <c r="V59" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="W59" s="2" t="s">
+      <c r="W59" s="8" t="s">
         <v>1104</v>
       </c>
       <c r="X59" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y59" s="2" t="s">
+      <c r="Y59" s="8" t="s">
         <v>770</v>
       </c>
-      <c r="Z59" s="2" t="s">
+      <c r="Z59" s="8" t="s">
         <v>769</v>
       </c>
       <c r="AA59" s="4" t="s">
@@ -15859,10 +16099,10 @@
       <c r="AE59" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AF59" s="4" t="s">
+      <c r="AF59" s="13" t="s">
         <v>1101</v>
       </c>
-      <c r="AG59" s="4" t="s">
+      <c r="AG59" s="13" t="s">
         <v>814</v>
       </c>
       <c r="AH59" s="2" t="s">
@@ -15880,7 +16120,7 @@
       <c r="AL59" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AM59" s="2" t="s">
+      <c r="AM59" s="8" t="s">
         <v>52</v>
       </c>
       <c r="AN59" s="2" t="s">
@@ -15918,6 +16158,10 @@
       <c r="F60" s="3" t="s">
         <v>1089</v>
       </c>
+      <c r="G60" s="8"/>
+      <c r="H60" s="11"/>
+      <c r="I60" s="11"/>
+      <c r="J60" s="11"/>
       <c r="K60" s="2" t="s">
         <v>1088</v>
       </c>
@@ -15948,16 +16192,16 @@
       <c r="V60" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W60" s="2" t="s">
+      <c r="W60" s="8" t="s">
         <v>1082</v>
       </c>
       <c r="X60" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y60" s="2" t="s">
+      <c r="Y60" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="Z60" s="2" t="s">
+      <c r="Z60" s="8" t="s">
         <v>357</v>
       </c>
       <c r="AA60" s="4" t="s">
@@ -15975,10 +16219,10 @@
       <c r="AE60" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF60" s="4" t="s">
+      <c r="AF60" s="13" t="s">
         <v>561</v>
       </c>
-      <c r="AG60" s="4" t="s">
+      <c r="AG60" s="13" t="s">
         <v>1080</v>
       </c>
       <c r="AH60" s="2" t="s">
@@ -15996,7 +16240,7 @@
       <c r="AL60" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="AM60" s="2" t="s">
+      <c r="AM60" s="8" t="s">
         <v>243</v>
       </c>
       <c r="AN60" s="2" t="s">
@@ -16034,6 +16278,10 @@
       <c r="F61" s="3" t="s">
         <v>1069</v>
       </c>
+      <c r="G61" s="8"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="11"/>
+      <c r="J61" s="11"/>
       <c r="K61" s="2" t="s">
         <v>622</v>
       </c>
@@ -16064,16 +16312,16 @@
       <c r="V61" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W61" s="2" t="s">
+      <c r="W61" s="8" t="s">
         <v>617</v>
       </c>
       <c r="X61" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="Y61" s="2" t="s">
+      <c r="Y61" s="8" t="s">
         <v>1065</v>
       </c>
-      <c r="Z61" s="2" t="s">
+      <c r="Z61" s="8" t="s">
         <v>615</v>
       </c>
       <c r="AA61" s="4" t="s">
@@ -16091,10 +16339,10 @@
       <c r="AE61" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AF61" s="4" t="s">
+      <c r="AF61" s="13" t="s">
         <v>561</v>
       </c>
-      <c r="AG61" s="4" t="s">
+      <c r="AG61" s="13" t="s">
         <v>791</v>
       </c>
       <c r="AH61" s="2" t="s">
@@ -16112,7 +16360,7 @@
       <c r="AL61" s="2" t="s">
         <v>1059</v>
       </c>
-      <c r="AM61" s="2" t="s">
+      <c r="AM61" s="8" t="s">
         <v>243</v>
       </c>
       <c r="AN61" s="2" t="s">
@@ -16150,6 +16398,10 @@
       <c r="F62" s="3" t="s">
         <v>1049</v>
       </c>
+      <c r="G62" s="8"/>
+      <c r="H62" s="11"/>
+      <c r="I62" s="11"/>
+      <c r="J62" s="11"/>
       <c r="K62" s="2" t="s">
         <v>1048</v>
       </c>
@@ -16180,16 +16432,16 @@
       <c r="V62" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="W62" s="2" t="s">
+      <c r="W62" s="8" t="s">
         <v>1042</v>
       </c>
       <c r="X62" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="Y62" s="2" t="s">
+      <c r="Y62" s="8" t="s">
         <v>770</v>
       </c>
-      <c r="Z62" s="2" t="s">
+      <c r="Z62" s="8" t="s">
         <v>769</v>
       </c>
       <c r="AA62" s="4" t="s">
@@ -16207,10 +16459,10 @@
       <c r="AE62" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AF62" s="4" t="s">
+      <c r="AF62" s="13" t="s">
         <v>637</v>
       </c>
-      <c r="AG62" s="4" t="s">
+      <c r="AG62" s="13" t="s">
         <v>733</v>
       </c>
       <c r="AH62" s="2" t="s">
@@ -16228,7 +16480,7 @@
       <c r="AL62" s="2" t="s">
         <v>1038</v>
       </c>
-      <c r="AM62" s="2" t="s">
+      <c r="AM62" s="8" t="s">
         <v>634</v>
       </c>
       <c r="AN62" s="2" t="s">
@@ -16266,6 +16518,10 @@
       <c r="F63" s="3" t="s">
         <v>1027</v>
       </c>
+      <c r="G63" s="8"/>
+      <c r="H63" s="11"/>
+      <c r="I63" s="11"/>
+      <c r="J63" s="11"/>
       <c r="K63" s="2" t="s">
         <v>1026</v>
       </c>
@@ -16296,16 +16552,16 @@
       <c r="V63" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W63" s="2" t="s">
+      <c r="W63" s="8" t="s">
         <v>708</v>
       </c>
       <c r="X63" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y63" s="2" t="s">
+      <c r="Y63" s="8" t="s">
         <v>1021</v>
       </c>
-      <c r="Z63" s="2" t="s">
+      <c r="Z63" s="8" t="s">
         <v>1020</v>
       </c>
       <c r="AA63" s="4" t="s">
@@ -16323,10 +16579,10 @@
       <c r="AE63" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AF63" s="4" t="s">
+      <c r="AF63" s="13" t="s">
         <v>706</v>
       </c>
-      <c r="AG63" s="4" t="s">
+      <c r="AG63" s="13" t="s">
         <v>561</v>
       </c>
       <c r="AH63" s="2" t="s">
@@ -16344,7 +16600,7 @@
       <c r="AL63" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="AM63" s="2">
+      <c r="AM63" s="8">
         <v>5</v>
       </c>
       <c r="AN63" s="2" t="s">
@@ -16382,6 +16638,10 @@
       <c r="F64" s="3" t="s">
         <v>1007</v>
       </c>
+      <c r="G64" s="8"/>
+      <c r="H64" s="11"/>
+      <c r="I64" s="11"/>
+      <c r="J64" s="11"/>
       <c r="K64" s="2" t="s">
         <v>1006</v>
       </c>
@@ -16412,16 +16672,16 @@
       <c r="V64" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="W64" s="2" t="s">
+      <c r="W64" s="8" t="s">
         <v>197</v>
       </c>
       <c r="X64" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="Y64" s="2" t="s">
+      <c r="Y64" s="8" t="s">
         <v>911</v>
       </c>
-      <c r="Z64" s="2" t="s">
+      <c r="Z64" s="8" t="s">
         <v>1000</v>
       </c>
       <c r="AA64" s="4" t="s">
@@ -16439,10 +16699,10 @@
       <c r="AE64" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AF64" s="4" t="s">
+      <c r="AF64" s="13" t="s">
         <v>460</v>
       </c>
-      <c r="AG64" s="4" t="s">
+      <c r="AG64" s="13" t="s">
         <v>637</v>
       </c>
       <c r="AH64" s="2" t="s">
@@ -16460,7 +16720,7 @@
       <c r="AL64" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="AM64" s="2" t="s">
+      <c r="AM64" s="8" t="s">
         <v>995</v>
       </c>
       <c r="AN64" s="2" t="s">
@@ -16498,6 +16758,10 @@
       <c r="F65" s="3" t="s">
         <v>984</v>
       </c>
+      <c r="G65" s="8"/>
+      <c r="H65" s="11"/>
+      <c r="I65" s="11"/>
+      <c r="J65" s="11"/>
       <c r="K65" s="2" t="s">
         <v>983</v>
       </c>
@@ -16528,16 +16792,16 @@
       <c r="V65" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="W65" s="2" t="s">
+      <c r="W65" s="8" t="s">
         <v>489</v>
       </c>
       <c r="X65" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y65" s="2" t="s">
+      <c r="Y65" s="8" t="s">
         <v>640</v>
       </c>
-      <c r="Z65" s="2" t="s">
+      <c r="Z65" s="8" t="s">
         <v>464</v>
       </c>
       <c r="AA65" s="4" t="s">
@@ -16555,10 +16819,10 @@
       <c r="AE65" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF65" s="4" t="s">
+      <c r="AF65" s="13" t="s">
         <v>486</v>
       </c>
-      <c r="AG65" s="4" t="s">
+      <c r="AG65" s="13" t="s">
         <v>561</v>
       </c>
       <c r="AH65" s="2" t="s">
@@ -16576,7 +16840,7 @@
       <c r="AL65" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="AM65" s="2" t="s">
+      <c r="AM65" s="8" t="s">
         <v>441</v>
       </c>
       <c r="AN65" s="2" t="s">
@@ -16614,6 +16878,10 @@
       <c r="F66" s="3" t="s">
         <v>965</v>
       </c>
+      <c r="G66" s="8"/>
+      <c r="H66" s="11"/>
+      <c r="I66" s="11"/>
+      <c r="J66" s="11"/>
       <c r="K66" s="2" t="s">
         <v>964</v>
       </c>
@@ -16644,7 +16912,7 @@
       <c r="V66" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="W66" s="2" t="s">
+      <c r="W66" s="8" t="s">
         <v>959</v>
       </c>
       <c r="X66" s="2" t="s">
@@ -16653,7 +16921,7 @@
       <c r="Y66" s="8" t="s">
         <v>958</v>
       </c>
-      <c r="Z66" s="2" t="s">
+      <c r="Z66" s="8" t="s">
         <v>957</v>
       </c>
       <c r="AA66" s="4" t="s">
@@ -16671,10 +16939,10 @@
       <c r="AE66" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="AF66" s="4" t="s">
+      <c r="AF66" s="13" t="s">
         <v>954</v>
       </c>
-      <c r="AG66" s="4" t="s">
+      <c r="AG66" s="13" t="s">
         <v>217</v>
       </c>
       <c r="AH66" s="2" t="s">
@@ -16692,7 +16960,7 @@
       <c r="AL66" s="2" t="s">
         <v>950</v>
       </c>
-      <c r="AM66" s="2" t="s">
+      <c r="AM66" s="8" t="s">
         <v>271</v>
       </c>
       <c r="AN66" s="2" t="s">
@@ -16730,6 +16998,10 @@
       <c r="F67" s="3" t="s">
         <v>939</v>
       </c>
+      <c r="G67" s="8"/>
+      <c r="H67" s="11"/>
+      <c r="I67" s="11"/>
+      <c r="J67" s="11"/>
       <c r="K67" s="2" t="s">
         <v>938</v>
       </c>
@@ -16760,16 +17032,16 @@
       <c r="V67" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="W67" s="2" t="s">
+      <c r="W67" s="8" t="s">
         <v>933</v>
       </c>
       <c r="X67" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y67" s="2" t="s">
+      <c r="Y67" s="8" t="s">
         <v>617</v>
       </c>
-      <c r="Z67" s="2" t="s">
+      <c r="Z67" s="8" t="s">
         <v>932</v>
       </c>
       <c r="AA67" s="4" t="s">
@@ -16787,10 +17059,10 @@
       <c r="AE67" s="4" t="s">
         <v>792</v>
       </c>
-      <c r="AF67" s="4" t="s">
+      <c r="AF67" s="13" t="s">
         <v>929</v>
       </c>
-      <c r="AG67" s="4" t="s">
+      <c r="AG67" s="13" t="s">
         <v>791</v>
       </c>
       <c r="AH67" s="2" t="s">
@@ -16808,7 +17080,7 @@
       <c r="AL67" s="2" t="s">
         <v>928</v>
       </c>
-      <c r="AM67" s="2" t="s">
+      <c r="AM67" s="8" t="s">
         <v>282</v>
       </c>
       <c r="AN67" s="2" t="s">
@@ -16846,6 +17118,10 @@
       <c r="F68" s="3" t="s">
         <v>918</v>
       </c>
+      <c r="G68" s="8"/>
+      <c r="H68" s="11"/>
+      <c r="I68" s="11"/>
+      <c r="J68" s="11"/>
       <c r="K68" s="2" t="s">
         <v>917</v>
       </c>
@@ -16876,16 +17152,16 @@
       <c r="V68" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="W68" s="2" t="s">
+      <c r="W68" s="8" t="s">
         <v>617</v>
       </c>
       <c r="X68" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y68" s="2" t="s">
+      <c r="Y68" s="8" t="s">
         <v>911</v>
       </c>
-      <c r="Z68" s="2" t="s">
+      <c r="Z68" s="8" t="s">
         <v>357</v>
       </c>
       <c r="AA68" s="4" t="s">
@@ -16903,10 +17179,10 @@
       <c r="AE68" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AF68" s="4" t="s">
+      <c r="AF68" s="13" t="s">
         <v>538</v>
       </c>
-      <c r="AG68" s="4" t="s">
+      <c r="AG68" s="13" t="s">
         <v>909</v>
       </c>
       <c r="AH68" s="2" t="s">
@@ -16924,7 +17200,7 @@
       <c r="AL68" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="AM68" s="2" t="s">
+      <c r="AM68" s="8" t="s">
         <v>241</v>
       </c>
       <c r="AN68" s="2" t="s">
@@ -16962,6 +17238,10 @@
       <c r="F69" s="3" t="s">
         <v>896</v>
       </c>
+      <c r="G69" s="8"/>
+      <c r="H69" s="11"/>
+      <c r="I69" s="11"/>
+      <c r="J69" s="11"/>
       <c r="K69" s="2" t="s">
         <v>895</v>
       </c>
@@ -16992,16 +17272,16 @@
       <c r="V69" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="W69" s="2" t="s">
+      <c r="W69" s="8" t="s">
         <v>890</v>
       </c>
       <c r="X69" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y69" s="2" t="s">
+      <c r="Y69" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="Z69" s="2" t="s">
+      <c r="Z69" s="8" t="s">
         <v>889</v>
       </c>
       <c r="AA69" s="4" t="s">
@@ -17019,10 +17299,10 @@
       <c r="AE69" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AF69" s="4" t="s">
+      <c r="AF69" s="13" t="s">
         <v>885</v>
       </c>
-      <c r="AG69" s="4" t="s">
+      <c r="AG69" s="13" t="s">
         <v>216</v>
       </c>
       <c r="AH69" s="2" t="s">
@@ -17040,7 +17320,7 @@
       <c r="AL69" s="2" t="s">
         <v>881</v>
       </c>
-      <c r="AM69" s="2" t="s">
+      <c r="AM69" s="8" t="s">
         <v>880</v>
       </c>
       <c r="AN69" s="2" t="s">
@@ -17078,6 +17358,10 @@
       <c r="F70" s="3" t="s">
         <v>869</v>
       </c>
+      <c r="G70" s="8"/>
+      <c r="H70" s="11"/>
+      <c r="I70" s="11"/>
+      <c r="J70" s="11"/>
       <c r="K70" s="2" t="s">
         <v>868</v>
       </c>
@@ -17108,16 +17392,16 @@
       <c r="V70" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W70" s="2" t="s">
+      <c r="W70" s="8" t="s">
         <v>862</v>
       </c>
       <c r="X70" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="Y70" s="7" t="s">
+      <c r="Y70" s="8" t="s">
         <v>861</v>
       </c>
-      <c r="Z70" s="2" t="s">
+      <c r="Z70" s="8" t="s">
         <v>816</v>
       </c>
       <c r="AA70" s="4" t="s">
@@ -17135,10 +17419,10 @@
       <c r="AE70" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AF70" s="4" t="s">
+      <c r="AF70" s="13" t="s">
         <v>460</v>
       </c>
-      <c r="AG70" s="4" t="s">
+      <c r="AG70" s="13" t="s">
         <v>309</v>
       </c>
       <c r="AH70" s="2" t="s">
@@ -17156,7 +17440,7 @@
       <c r="AL70" s="2" t="s">
         <v>856</v>
       </c>
-      <c r="AM70" s="2" t="s">
+      <c r="AM70" s="8" t="s">
         <v>243</v>
       </c>
       <c r="AN70" s="2" t="s">
@@ -17194,6 +17478,10 @@
       <c r="F71" s="3" t="s">
         <v>845</v>
       </c>
+      <c r="G71" s="8"/>
+      <c r="H71" s="11"/>
+      <c r="I71" s="11"/>
+      <c r="J71" s="11"/>
       <c r="K71" s="2" t="s">
         <v>76</v>
       </c>
@@ -17224,16 +17512,16 @@
       <c r="V71" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="W71" s="2" t="s">
+      <c r="W71" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X71" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y71" s="2" t="s">
+      <c r="Y71" s="8" t="s">
         <v>840</v>
       </c>
-      <c r="Z71" s="2" t="s">
+      <c r="Z71" s="8" t="s">
         <v>752</v>
       </c>
       <c r="AA71" s="4" t="s">
@@ -17251,10 +17539,10 @@
       <c r="AE71" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AF71" s="4" t="s">
+      <c r="AF71" s="13" t="s">
         <v>838</v>
       </c>
-      <c r="AG71" s="4" t="s">
+      <c r="AG71" s="13" t="s">
         <v>837</v>
       </c>
       <c r="AH71" s="2" t="s">
@@ -17272,7 +17560,7 @@
       <c r="AL71" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="AM71" s="2" t="s">
+      <c r="AM71" s="8" t="s">
         <v>52</v>
       </c>
       <c r="AN71" s="2" t="s">
@@ -17310,6 +17598,10 @@
       <c r="F72" s="3" t="s">
         <v>825</v>
       </c>
+      <c r="G72" s="8"/>
+      <c r="H72" s="11"/>
+      <c r="I72" s="11"/>
+      <c r="J72" s="11"/>
       <c r="K72" s="2" t="s">
         <v>824</v>
       </c>
@@ -17340,16 +17632,16 @@
       <c r="V72" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W72" s="2" t="s">
+      <c r="W72" s="8" t="s">
         <v>818</v>
       </c>
       <c r="X72" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="Y72" s="2" t="s">
+      <c r="Y72" s="8" t="s">
         <v>817</v>
       </c>
-      <c r="Z72" s="2" t="s">
+      <c r="Z72" s="8" t="s">
         <v>816</v>
       </c>
       <c r="AA72" s="4" t="s">
@@ -17367,10 +17659,10 @@
       <c r="AE72" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AF72" s="4" t="s">
+      <c r="AF72" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="AG72" s="4" t="s">
+      <c r="AG72" s="13" t="s">
         <v>814</v>
       </c>
       <c r="AH72" s="2" t="s">
@@ -17388,7 +17680,7 @@
       <c r="AL72" s="2" t="s">
         <v>811</v>
       </c>
-      <c r="AM72" s="2" t="s">
+      <c r="AM72" s="8" t="s">
         <v>241</v>
       </c>
       <c r="AN72" s="2" t="s">
@@ -17426,6 +17718,10 @@
       <c r="F73" s="3" t="s">
         <v>800</v>
       </c>
+      <c r="G73" s="8"/>
+      <c r="H73" s="11"/>
+      <c r="I73" s="11"/>
+      <c r="J73" s="11"/>
       <c r="K73" s="2" t="s">
         <v>799</v>
       </c>
@@ -17456,16 +17752,16 @@
       <c r="V73" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W73" s="2" t="s">
+      <c r="W73" s="8" t="s">
         <v>795</v>
       </c>
       <c r="X73" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="Y73" s="2" t="s">
+      <c r="Y73" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="Z73" s="2" t="s">
+      <c r="Z73" s="8" t="s">
         <v>794</v>
       </c>
       <c r="AA73" s="4" t="s">
@@ -17483,10 +17779,10 @@
       <c r="AE73" s="4" t="s">
         <v>792</v>
       </c>
-      <c r="AF73" s="4" t="s">
+      <c r="AF73" s="13" t="s">
         <v>791</v>
       </c>
-      <c r="AG73" s="4" t="s">
+      <c r="AG73" s="13" t="s">
         <v>790</v>
       </c>
       <c r="AH73" s="2" t="s">
@@ -17504,7 +17800,7 @@
       <c r="AL73" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="AM73" s="2" t="s">
+      <c r="AM73" s="8" t="s">
         <v>787</v>
       </c>
       <c r="AN73" s="2" t="s">
@@ -17542,6 +17838,10 @@
       <c r="F74" s="3" t="s">
         <v>777</v>
       </c>
+      <c r="G74" s="8"/>
+      <c r="H74" s="11"/>
+      <c r="I74" s="11"/>
+      <c r="J74" s="11"/>
       <c r="K74" s="2" t="s">
         <v>776</v>
       </c>
@@ -17572,16 +17872,16 @@
       <c r="V74" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W74" s="2" t="s">
+      <c r="W74" s="8" t="s">
         <v>771</v>
       </c>
       <c r="X74" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y74" s="2" t="s">
+      <c r="Y74" s="8" t="s">
         <v>770</v>
       </c>
-      <c r="Z74" s="2" t="s">
+      <c r="Z74" s="8" t="s">
         <v>769</v>
       </c>
       <c r="AA74" s="4" t="s">
@@ -17599,10 +17899,10 @@
       <c r="AE74" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF74" s="4" t="s">
+      <c r="AF74" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="AG74" s="4" t="s">
+      <c r="AG74" s="13" t="s">
         <v>352</v>
       </c>
       <c r="AH74" s="2" t="s">
@@ -17620,7 +17920,7 @@
       <c r="AL74" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="AM74" s="2">
+      <c r="AM74" s="8">
         <v>5</v>
       </c>
       <c r="AN74" s="2" t="s">
@@ -17658,6 +17958,10 @@
       <c r="F75" s="3" t="s">
         <v>756</v>
       </c>
+      <c r="G75" s="8"/>
+      <c r="H75" s="11"/>
+      <c r="I75" s="11"/>
+      <c r="J75" s="11"/>
       <c r="K75" s="2" t="s">
         <v>76</v>
       </c>
@@ -17688,16 +17992,16 @@
       <c r="V75" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="W75" s="2" t="s">
+      <c r="W75" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X75" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y75" s="2" t="s">
+      <c r="Y75" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="Z75" s="2" t="s">
+      <c r="Z75" s="8" t="s">
         <v>752</v>
       </c>
       <c r="AA75" s="4" t="s">
@@ -17715,10 +18019,10 @@
       <c r="AE75" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF75" s="4" t="s">
+      <c r="AF75" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="AG75" s="4" t="s">
+      <c r="AG75" s="13" t="s">
         <v>190</v>
       </c>
       <c r="AH75" s="2" t="s">
@@ -17736,7 +18040,7 @@
       <c r="AL75" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="AM75" s="2" t="s">
+      <c r="AM75" s="8" t="s">
         <v>243</v>
       </c>
       <c r="AN75" s="2" t="s">
@@ -17774,6 +18078,10 @@
       <c r="F76" s="3" t="s">
         <v>739</v>
       </c>
+      <c r="G76" s="8"/>
+      <c r="H76" s="11"/>
+      <c r="I76" s="11"/>
+      <c r="J76" s="11"/>
       <c r="K76" s="2" t="s">
         <v>738</v>
       </c>
@@ -17804,16 +18112,16 @@
       <c r="V76" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="W76" s="2" t="s">
+      <c r="W76" s="8" t="s">
         <v>732</v>
       </c>
       <c r="X76" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y76" s="2" t="s">
+      <c r="Y76" s="8" t="s">
         <v>731</v>
       </c>
-      <c r="Z76" s="2" t="s">
+      <c r="Z76" s="8" t="s">
         <v>730</v>
       </c>
       <c r="AA76" s="4" t="s">
@@ -17831,10 +18139,10 @@
       <c r="AE76" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AF76" s="4" t="s">
+      <c r="AF76" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="AG76" s="4" t="s">
+      <c r="AG76" s="13" t="s">
         <v>93</v>
       </c>
       <c r="AH76" s="2" t="s">
@@ -17852,7 +18160,7 @@
       <c r="AL76" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="AM76" s="2" t="s">
+      <c r="AM76" s="8" t="s">
         <v>642</v>
       </c>
       <c r="AN76" s="2" t="s">
@@ -17890,6 +18198,10 @@
       <c r="F77" s="3" t="s">
         <v>714</v>
       </c>
+      <c r="G77" s="8"/>
+      <c r="H77" s="11"/>
+      <c r="I77" s="11"/>
+      <c r="J77" s="11"/>
       <c r="K77" s="2" t="s">
         <v>713</v>
       </c>
@@ -17920,16 +18232,16 @@
       <c r="V77" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="W77" s="2" t="s">
+      <c r="W77" s="8" t="s">
         <v>542</v>
       </c>
       <c r="X77" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y77" s="2" t="s">
+      <c r="Y77" s="8" t="s">
         <v>708</v>
       </c>
-      <c r="Z77" s="2" t="s">
+      <c r="Z77" s="8" t="s">
         <v>411</v>
       </c>
       <c r="AA77" s="4" t="s">
@@ -17947,10 +18259,10 @@
       <c r="AE77" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF77" s="4" t="s">
+      <c r="AF77" s="13" t="s">
         <v>706</v>
       </c>
-      <c r="AG77" s="4" t="s">
+      <c r="AG77" s="13" t="s">
         <v>705</v>
       </c>
       <c r="AH77" s="2" t="s">
@@ -17968,7 +18280,7 @@
       <c r="AL77" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="AM77" s="2" t="s">
+      <c r="AM77" s="8" t="s">
         <v>678</v>
       </c>
       <c r="AN77" s="2" t="s">
@@ -18006,6 +18318,10 @@
       <c r="F78" s="3" t="s">
         <v>693</v>
       </c>
+      <c r="G78" s="8"/>
+      <c r="H78" s="11"/>
+      <c r="I78" s="11"/>
+      <c r="J78" s="11"/>
       <c r="K78" s="2" t="s">
         <v>692</v>
       </c>
@@ -18036,16 +18352,16 @@
       <c r="V78" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="W78" s="2" t="s">
+      <c r="W78" s="8" t="s">
         <v>686</v>
       </c>
       <c r="X78" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y78" s="2" t="s">
+      <c r="Y78" s="8" t="s">
         <v>685</v>
       </c>
-      <c r="Z78" s="2" t="s">
+      <c r="Z78" s="8" t="s">
         <v>684</v>
       </c>
       <c r="AA78" s="4" t="s">
@@ -18063,10 +18379,10 @@
       <c r="AE78" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF78" s="4" t="s">
+      <c r="AF78" s="13" t="s">
         <v>486</v>
       </c>
-      <c r="AG78" s="4" t="s">
+      <c r="AG78" s="13" t="s">
         <v>191</v>
       </c>
       <c r="AH78" s="2" t="s">
@@ -18084,7 +18400,7 @@
       <c r="AL78" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="AM78" s="2" t="s">
+      <c r="AM78" s="8" t="s">
         <v>678</v>
       </c>
       <c r="AN78" s="2" t="s">
@@ -18122,6 +18438,10 @@
       <c r="F79" s="3" t="s">
         <v>668</v>
       </c>
+      <c r="G79" s="8"/>
+      <c r="H79" s="11"/>
+      <c r="I79" s="11"/>
+      <c r="J79" s="11"/>
       <c r="K79" s="2" t="s">
         <v>667</v>
       </c>
@@ -18152,16 +18472,16 @@
       <c r="V79" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W79" s="2" t="s">
+      <c r="W79" s="8" t="s">
         <v>542</v>
       </c>
       <c r="X79" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y79" s="2" t="s">
+      <c r="Y79" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="Z79" s="2" t="s">
+      <c r="Z79" s="8" t="s">
         <v>357</v>
       </c>
       <c r="AA79" s="4" t="s">
@@ -18179,10 +18499,10 @@
       <c r="AE79" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF79" s="4" t="s">
+      <c r="AF79" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="AG79" s="4" t="s">
+      <c r="AG79" s="13" t="s">
         <v>351</v>
       </c>
       <c r="AH79" s="2" t="s">
@@ -18200,7 +18520,7 @@
       <c r="AL79" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AM79" s="2">
+      <c r="AM79" s="8">
         <v>3</v>
       </c>
       <c r="AN79" s="2" t="s">
@@ -18238,6 +18558,10 @@
       <c r="F80" s="3" t="s">
         <v>649</v>
       </c>
+      <c r="G80" s="8"/>
+      <c r="H80" s="11"/>
+      <c r="I80" s="11"/>
+      <c r="J80" s="11"/>
       <c r="K80" s="2" t="s">
         <v>648</v>
       </c>
@@ -18268,16 +18592,16 @@
       <c r="V80" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="W80" s="2" t="s">
+      <c r="W80" s="8" t="s">
         <v>641</v>
       </c>
       <c r="X80" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y80" s="2" t="s">
+      <c r="Y80" s="8" t="s">
         <v>640</v>
       </c>
-      <c r="Z80" s="2" t="s">
+      <c r="Z80" s="8" t="s">
         <v>385</v>
       </c>
       <c r="AA80" s="4" t="s">
@@ -18295,10 +18619,10 @@
       <c r="AE80" s="4" t="s">
         <v>638</v>
       </c>
-      <c r="AF80" s="4" t="s">
+      <c r="AF80" s="13" t="s">
         <v>637</v>
       </c>
-      <c r="AG80" s="4" t="s">
+      <c r="AG80" s="13" t="s">
         <v>309</v>
       </c>
       <c r="AH80" s="2" t="s">
@@ -18316,7 +18640,7 @@
       <c r="AL80" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="AM80" s="2" t="s">
+      <c r="AM80" s="8" t="s">
         <v>634</v>
       </c>
       <c r="AN80" s="2" t="s">
@@ -18354,6 +18678,10 @@
       <c r="F81" s="3" t="s">
         <v>623</v>
       </c>
+      <c r="G81" s="8"/>
+      <c r="H81" s="11"/>
+      <c r="I81" s="11"/>
+      <c r="J81" s="11"/>
       <c r="K81" s="2" t="s">
         <v>622</v>
       </c>
@@ -18384,16 +18712,16 @@
       <c r="V81" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W81" s="2" t="s">
+      <c r="W81" s="8" t="s">
         <v>617</v>
       </c>
       <c r="X81" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="Y81" s="2" t="s">
+      <c r="Y81" s="8" t="s">
         <v>616</v>
       </c>
-      <c r="Z81" s="2" t="s">
+      <c r="Z81" s="8" t="s">
         <v>615</v>
       </c>
       <c r="AA81" s="4" t="s">
@@ -18411,10 +18739,10 @@
       <c r="AE81" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AF81" s="4" t="s">
+      <c r="AF81" s="13" t="s">
         <v>408</v>
       </c>
-      <c r="AG81" s="4" t="s">
+      <c r="AG81" s="13" t="s">
         <v>309</v>
       </c>
       <c r="AH81" s="2" t="s">
@@ -18432,7 +18760,7 @@
       <c r="AL81" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="AM81" s="2">
+      <c r="AM81" s="8">
         <v>2</v>
       </c>
       <c r="AN81" s="2" t="s">
@@ -18470,6 +18798,10 @@
       <c r="F82" s="3" t="s">
         <v>598</v>
       </c>
+      <c r="G82" s="8"/>
+      <c r="H82" s="11"/>
+      <c r="I82" s="11"/>
+      <c r="J82" s="11"/>
       <c r="K82" s="2" t="s">
         <v>76</v>
       </c>
@@ -18500,16 +18832,16 @@
       <c r="V82" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="W82" s="2" t="s">
+      <c r="W82" s="8" t="s">
         <v>440</v>
       </c>
       <c r="X82" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y82" s="2" t="s">
+      <c r="Y82" s="8" t="s">
         <v>593</v>
       </c>
-      <c r="Z82" s="2" t="s">
+      <c r="Z82" s="8" t="s">
         <v>438</v>
       </c>
       <c r="AA82" s="4" t="s">
@@ -18527,10 +18859,10 @@
       <c r="AE82" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AF82" s="4" t="s">
+      <c r="AF82" s="13" t="s">
         <v>590</v>
       </c>
-      <c r="AG82" s="4" t="s">
+      <c r="AG82" s="13" t="s">
         <v>589</v>
       </c>
       <c r="AH82" s="2" t="s">
@@ -18548,7 +18880,7 @@
       <c r="AL82" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="AM82" s="2" t="s">
+      <c r="AM82" s="8" t="s">
         <v>585</v>
       </c>
       <c r="AN82" s="2" t="s">
@@ -18586,6 +18918,10 @@
       <c r="F83" s="3" t="s">
         <v>574</v>
       </c>
+      <c r="G83" s="8"/>
+      <c r="H83" s="11"/>
+      <c r="I83" s="11"/>
+      <c r="J83" s="11"/>
       <c r="K83" s="2" t="s">
         <v>573</v>
       </c>
@@ -18616,16 +18952,16 @@
       <c r="V83" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="W83" s="2" t="s">
+      <c r="W83" s="8" t="s">
         <v>567</v>
       </c>
       <c r="X83" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y83" s="2" t="s">
+      <c r="Y83" s="8" t="s">
         <v>566</v>
       </c>
-      <c r="Z83" s="2" t="s">
+      <c r="Z83" s="8" t="s">
         <v>565</v>
       </c>
       <c r="AA83" s="4" t="s">
@@ -18643,10 +18979,10 @@
       <c r="AE83" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF83" s="4" t="s">
+      <c r="AF83" s="13" t="s">
         <v>562</v>
       </c>
-      <c r="AG83" s="4" t="s">
+      <c r="AG83" s="13" t="s">
         <v>561</v>
       </c>
       <c r="AH83" s="2" t="s">
@@ -18664,7 +19000,7 @@
       <c r="AL83" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="AM83" s="2" t="s">
+      <c r="AM83" s="8" t="s">
         <v>482</v>
       </c>
       <c r="AN83" s="2" t="s">
@@ -18702,6 +19038,10 @@
       <c r="F84" s="3" t="s">
         <v>548</v>
       </c>
+      <c r="G84" s="8"/>
+      <c r="H84" s="11"/>
+      <c r="I84" s="11"/>
+      <c r="J84" s="11"/>
       <c r="K84" s="2" t="s">
         <v>547</v>
       </c>
@@ -18732,16 +19072,16 @@
       <c r="V84" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="W84" s="2" t="s">
+      <c r="W84" s="8" t="s">
         <v>542</v>
       </c>
       <c r="X84" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y84" s="2" t="s">
+      <c r="Y84" s="8" t="s">
         <v>541</v>
       </c>
-      <c r="Z84" s="2" t="s">
+      <c r="Z84" s="8" t="s">
         <v>411</v>
       </c>
       <c r="AA84" s="4" t="s">
@@ -18759,10 +19099,10 @@
       <c r="AE84" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF84" s="4" t="s">
+      <c r="AF84" s="13" t="s">
         <v>538</v>
       </c>
-      <c r="AG84" s="4" t="s">
+      <c r="AG84" s="13" t="s">
         <v>160</v>
       </c>
       <c r="AH84" s="2" t="s">
@@ -18780,7 +19120,7 @@
       <c r="AL84" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="AM84" s="2" t="s">
+      <c r="AM84" s="8" t="s">
         <v>534</v>
       </c>
       <c r="AN84" s="2" t="s">
@@ -18818,6 +19158,10 @@
       <c r="F85" s="3" t="s">
         <v>524</v>
       </c>
+      <c r="G85" s="8"/>
+      <c r="H85" s="11"/>
+      <c r="I85" s="11"/>
+      <c r="J85" s="11"/>
       <c r="K85" s="2" t="s">
         <v>523</v>
       </c>
@@ -18848,16 +19192,16 @@
       <c r="V85" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="W85" s="2" t="s">
+      <c r="W85" s="8" t="s">
         <v>517</v>
       </c>
       <c r="X85" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y85" s="2" t="s">
+      <c r="Y85" s="8" t="s">
         <v>516</v>
       </c>
-      <c r="Z85" s="2" t="s">
+      <c r="Z85" s="8" t="s">
         <v>515</v>
       </c>
       <c r="AA85" s="4" t="s">
@@ -18875,10 +19219,10 @@
       <c r="AE85" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AF85" s="4" t="s">
+      <c r="AF85" s="13" t="s">
         <v>512</v>
       </c>
-      <c r="AG85" s="4" t="s">
+      <c r="AG85" s="13" t="s">
         <v>511</v>
       </c>
       <c r="AH85" s="2" t="s">
@@ -18896,7 +19240,7 @@
       <c r="AL85" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="AM85" s="2" t="s">
+      <c r="AM85" s="8" t="s">
         <v>506</v>
       </c>
       <c r="AN85" s="2" t="s">
@@ -18934,6 +19278,10 @@
       <c r="F86" s="3" t="s">
         <v>495</v>
       </c>
+      <c r="G86" s="8"/>
+      <c r="H86" s="11"/>
+      <c r="I86" s="11"/>
+      <c r="J86" s="11"/>
       <c r="K86" s="2" t="s">
         <v>494</v>
       </c>
@@ -18964,16 +19312,16 @@
       <c r="V86" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="W86" s="2" t="s">
+      <c r="W86" s="8" t="s">
         <v>489</v>
       </c>
       <c r="X86" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y86" s="2" t="s">
+      <c r="Y86" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="Z86" s="2" t="s">
+      <c r="Z86" s="8" t="s">
         <v>464</v>
       </c>
       <c r="AA86" s="4" t="s">
@@ -18991,10 +19339,10 @@
       <c r="AE86" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF86" s="4" t="s">
+      <c r="AF86" s="13" t="s">
         <v>486</v>
       </c>
-      <c r="AG86" s="4" t="s">
+      <c r="AG86" s="13" t="s">
         <v>191</v>
       </c>
       <c r="AH86" s="2" t="s">
@@ -19012,7 +19360,7 @@
       <c r="AL86" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="AM86" s="2" t="s">
+      <c r="AM86" s="8" t="s">
         <v>482</v>
       </c>
       <c r="AN86" s="2" t="s">
@@ -19050,6 +19398,10 @@
       <c r="F87" s="3" t="s">
         <v>472</v>
       </c>
+      <c r="G87" s="8"/>
+      <c r="H87" s="11"/>
+      <c r="I87" s="11"/>
+      <c r="J87" s="11"/>
       <c r="K87" s="2" t="s">
         <v>471</v>
       </c>
@@ -19080,16 +19432,16 @@
       <c r="V87" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="W87" s="2" t="s">
+      <c r="W87" s="8" t="s">
         <v>465</v>
       </c>
       <c r="X87" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y87" s="2" t="s">
+      <c r="Y87" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="Z87" s="2" t="s">
+      <c r="Z87" s="8" t="s">
         <v>464</v>
       </c>
       <c r="AA87" s="4" t="s">
@@ -19107,10 +19459,10 @@
       <c r="AE87" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AF87" s="4" t="s">
+      <c r="AF87" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="AG87" s="4" t="s">
+      <c r="AG87" s="13" t="s">
         <v>460</v>
       </c>
       <c r="AH87" s="2" t="s">
@@ -19128,7 +19480,7 @@
       <c r="AL87" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="AM87" s="2" t="s">
+      <c r="AM87" s="8" t="s">
         <v>102</v>
       </c>
       <c r="AN87" s="2" t="s">
@@ -19166,6 +19518,10 @@
       <c r="F88" s="3" t="s">
         <v>448</v>
       </c>
+      <c r="G88" s="8"/>
+      <c r="H88" s="11"/>
+      <c r="I88" s="11"/>
+      <c r="J88" s="11"/>
       <c r="K88" s="2" t="s">
         <v>76</v>
       </c>
@@ -19196,16 +19552,16 @@
       <c r="V88" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="W88" s="2" t="s">
+      <c r="W88" s="8" t="s">
         <v>440</v>
       </c>
       <c r="X88" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y88" s="2" t="s">
+      <c r="Y88" s="8" t="s">
         <v>439</v>
       </c>
-      <c r="Z88" s="2" t="s">
+      <c r="Z88" s="8" t="s">
         <v>438</v>
       </c>
       <c r="AA88" s="4" t="s">
@@ -19223,10 +19579,10 @@
       <c r="AE88" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="AF88" s="4" t="s">
+      <c r="AF88" s="13" t="s">
         <v>435</v>
       </c>
-      <c r="AG88" s="4" t="s">
+      <c r="AG88" s="13" t="s">
         <v>217</v>
       </c>
       <c r="AH88" s="2" t="s">
@@ -19244,7 +19600,7 @@
       <c r="AL88" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="AM88" s="2" t="s">
+      <c r="AM88" s="8" t="s">
         <v>431</v>
       </c>
       <c r="AN88" s="2" t="s">
@@ -19282,6 +19638,10 @@
       <c r="F89" s="3" t="s">
         <v>420</v>
       </c>
+      <c r="G89" s="8"/>
+      <c r="H89" s="11"/>
+      <c r="I89" s="11"/>
+      <c r="J89" s="11"/>
       <c r="K89" s="2" t="s">
         <v>419</v>
       </c>
@@ -19312,16 +19672,16 @@
       <c r="V89" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="W89" s="2" t="s">
+      <c r="W89" s="8" t="s">
         <v>413</v>
       </c>
       <c r="X89" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y89" s="2" t="s">
+      <c r="Y89" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="Z89" s="2" t="s">
+      <c r="Z89" s="8" t="s">
         <v>411</v>
       </c>
       <c r="AA89" s="4" t="s">
@@ -19339,10 +19699,10 @@
       <c r="AE89" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AF89" s="4" t="s">
+      <c r="AF89" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="AG89" s="4" t="s">
+      <c r="AG89" s="13" t="s">
         <v>408</v>
       </c>
       <c r="AH89" s="2" t="s">
@@ -19360,7 +19720,7 @@
       <c r="AL89" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="AM89" s="2" t="s">
+      <c r="AM89" s="8" t="s">
         <v>88</v>
       </c>
       <c r="AN89" s="2" t="s">
@@ -19398,6 +19758,10 @@
       <c r="F90" s="3" t="s">
         <v>394</v>
       </c>
+      <c r="G90" s="8"/>
+      <c r="H90" s="11"/>
+      <c r="I90" s="11"/>
+      <c r="J90" s="11"/>
       <c r="K90" s="2" t="s">
         <v>393</v>
       </c>
@@ -19428,16 +19792,16 @@
       <c r="V90" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="W90" s="2" t="s">
+      <c r="W90" s="8" t="s">
         <v>387</v>
       </c>
       <c r="X90" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y90" s="2" t="s">
+      <c r="Y90" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="Z90" s="2" t="s">
+      <c r="Z90" s="8" t="s">
         <v>385</v>
       </c>
       <c r="AA90" s="4" t="s">
@@ -19455,10 +19819,10 @@
       <c r="AE90" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF90" s="4" t="s">
+      <c r="AF90" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="AG90" s="4" t="s">
+      <c r="AG90" s="13" t="s">
         <v>381</v>
       </c>
       <c r="AH90" s="2" t="s">
@@ -19476,7 +19840,7 @@
       <c r="AL90" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="AM90" s="2" t="s">
+      <c r="AM90" s="8" t="s">
         <v>377</v>
       </c>
       <c r="AN90" s="2" t="s">
@@ -19514,6 +19878,10 @@
       <c r="F91" s="3" t="s">
         <v>366</v>
       </c>
+      <c r="G91" s="8"/>
+      <c r="H91" s="11"/>
+      <c r="I91" s="11"/>
+      <c r="J91" s="11"/>
       <c r="K91" s="2" t="s">
         <v>365</v>
       </c>
@@ -19544,16 +19912,16 @@
       <c r="V91" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W91" s="2" t="s">
+      <c r="W91" s="8" t="s">
         <v>359</v>
       </c>
       <c r="X91" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y91" s="2" t="s">
+      <c r="Y91" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="Z91" s="2" t="s">
+      <c r="Z91" s="8" t="s">
         <v>357</v>
       </c>
       <c r="AA91" s="4" t="s">
@@ -19571,10 +19939,10 @@
       <c r="AE91" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF91" s="4" t="s">
+      <c r="AF91" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="AG91" s="4" t="s">
+      <c r="AG91" s="13" t="s">
         <v>351</v>
       </c>
       <c r="AH91" s="2" t="s">
@@ -19592,7 +19960,7 @@
       <c r="AL91" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="AM91" s="2">
+      <c r="AM91" s="8">
         <v>1</v>
       </c>
       <c r="AN91" s="2" t="s">
@@ -19630,6 +19998,10 @@
       <c r="F92" s="3" t="s">
         <v>338</v>
       </c>
+      <c r="G92" s="8"/>
+      <c r="H92" s="11"/>
+      <c r="I92" s="11"/>
+      <c r="J92" s="11"/>
       <c r="K92" s="2" t="s">
         <v>76</v>
       </c>
@@ -19660,16 +20032,16 @@
       <c r="V92" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="W92" s="2" t="s">
+      <c r="W92" s="8" t="s">
         <v>331</v>
       </c>
       <c r="X92" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y92" s="2" t="s">
+      <c r="Y92" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="Z92" s="2" t="s">
+      <c r="Z92" s="8" t="s">
         <v>306</v>
       </c>
       <c r="AA92" s="4" t="s">
@@ -19687,10 +20059,10 @@
       <c r="AE92" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AF92" s="4" t="s">
+      <c r="AF92" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="AG92" s="4" t="s">
+      <c r="AG92" s="13" t="s">
         <v>93</v>
       </c>
       <c r="AH92" s="2" t="s">
@@ -19708,7 +20080,7 @@
       <c r="AL92" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AM92" s="2" t="s">
+      <c r="AM92" s="8" t="s">
         <v>102</v>
       </c>
       <c r="AN92" s="2" t="s">
@@ -19746,6 +20118,10 @@
       <c r="F93" s="3" t="s">
         <v>316</v>
       </c>
+      <c r="G93" s="8"/>
+      <c r="H93" s="11"/>
+      <c r="I93" s="11"/>
+      <c r="J93" s="11"/>
       <c r="K93" s="2" t="s">
         <v>315</v>
       </c>
@@ -19776,16 +20152,16 @@
       <c r="V93" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="W93" s="2" t="s">
+      <c r="W93" s="8" t="s">
         <v>308</v>
       </c>
       <c r="X93" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y93" s="2" t="s">
+      <c r="Y93" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="Z93" s="2" t="s">
+      <c r="Z93" s="8" t="s">
         <v>306</v>
       </c>
       <c r="AA93" s="4" t="s">
@@ -19803,10 +20179,10 @@
       <c r="AE93" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="AF93" s="4" t="s">
+      <c r="AF93" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="AG93" s="4" t="s">
+      <c r="AG93" s="13" t="s">
         <v>303</v>
       </c>
       <c r="AH93" s="2" t="s">
@@ -19824,7 +20200,7 @@
       <c r="AL93" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="AM93" s="2" t="s">
+      <c r="AM93" s="8" t="s">
         <v>299</v>
       </c>
       <c r="AN93" s="2" t="s">
@@ -19862,6 +20238,10 @@
       <c r="F94" s="3" t="s">
         <v>288</v>
       </c>
+      <c r="G94" s="8"/>
+      <c r="H94" s="11"/>
+      <c r="I94" s="11"/>
+      <c r="J94" s="11"/>
       <c r="K94" s="2" t="s">
         <v>287</v>
       </c>
@@ -19892,16 +20272,16 @@
       <c r="V94" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="W94" s="2" t="s">
+      <c r="W94" s="8" t="s">
         <v>281</v>
       </c>
       <c r="X94" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Y94" s="2" t="s">
+      <c r="Y94" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="Z94" s="2" t="s">
+      <c r="Z94" s="8" t="s">
         <v>279</v>
       </c>
       <c r="AA94" s="4" t="s">
@@ -19919,10 +20299,10 @@
       <c r="AE94" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AF94" s="4" t="s">
+      <c r="AF94" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="AG94" s="4" t="s">
+      <c r="AG94" s="13" t="s">
         <v>160</v>
       </c>
       <c r="AH94" s="2" t="s">
@@ -19940,7 +20320,7 @@
       <c r="AL94" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="AM94" s="2" t="s">
+      <c r="AM94" s="8" t="s">
         <v>271</v>
       </c>
       <c r="AN94" s="2" t="s">
@@ -19978,6 +20358,10 @@
       <c r="F95" s="3" t="s">
         <v>260</v>
       </c>
+      <c r="G95" s="8"/>
+      <c r="H95" s="11"/>
+      <c r="I95" s="11"/>
+      <c r="J95" s="11"/>
       <c r="K95" s="2" t="s">
         <v>76</v>
       </c>
@@ -20008,16 +20392,16 @@
       <c r="V95" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="W95" s="2" t="s">
+      <c r="W95" s="8" t="s">
         <v>253</v>
       </c>
       <c r="X95" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y95" s="2" t="s">
+      <c r="Y95" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="Z95" s="2" t="s">
+      <c r="Z95" s="8" t="s">
         <v>63</v>
       </c>
       <c r="AA95" s="4" t="s">
@@ -20035,10 +20419,10 @@
       <c r="AE95" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="AF95" s="4" t="s">
+      <c r="AF95" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="AG95" s="4" t="s">
+      <c r="AG95" s="13" t="s">
         <v>246</v>
       </c>
       <c r="AH95" s="2" t="s">
@@ -20056,7 +20440,7 @@
       <c r="AL95" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="AM95" s="2" t="s">
+      <c r="AM95" s="8" t="s">
         <v>241</v>
       </c>
       <c r="AN95" s="2" t="s">
@@ -20094,6 +20478,10 @@
       <c r="F96" s="3" t="s">
         <v>230</v>
       </c>
+      <c r="G96" s="8"/>
+      <c r="H96" s="11"/>
+      <c r="I96" s="11"/>
+      <c r="J96" s="11"/>
       <c r="K96" s="2" t="s">
         <v>229</v>
       </c>
@@ -20124,16 +20512,16 @@
       <c r="V96" s="2">
         <v>85</v>
       </c>
-      <c r="W96" s="2" t="s">
+      <c r="W96" s="8" t="s">
         <v>223</v>
       </c>
       <c r="X96" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="Y96" s="2" t="s">
+      <c r="Y96" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="Z96" s="2" t="s">
+      <c r="Z96" s="8" t="s">
         <v>221</v>
       </c>
       <c r="AA96" s="4" t="s">
@@ -20151,10 +20539,10 @@
       <c r="AE96" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="AF96" s="4" t="s">
+      <c r="AF96" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="AG96" s="4" t="s">
+      <c r="AG96" s="13" t="s">
         <v>216</v>
       </c>
       <c r="AH96" s="6">
@@ -20172,7 +20560,7 @@
       <c r="AL96" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="AM96" s="2">
+      <c r="AM96" s="8">
         <v>40</v>
       </c>
       <c r="AN96" s="2" t="s">
@@ -20210,6 +20598,10 @@
       <c r="F97" s="3" t="s">
         <v>205</v>
       </c>
+      <c r="G97" s="8"/>
+      <c r="H97" s="11"/>
+      <c r="I97" s="11"/>
+      <c r="J97" s="11"/>
       <c r="K97" s="2" t="s">
         <v>204</v>
       </c>
@@ -20240,16 +20632,16 @@
       <c r="V97" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="W97" s="2" t="s">
+      <c r="W97" s="8" t="s">
         <v>197</v>
       </c>
       <c r="X97" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y97" s="2" t="s">
+      <c r="Y97" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="Z97" s="2" t="s">
+      <c r="Z97" s="8" t="s">
         <v>195</v>
       </c>
       <c r="AA97" s="4" t="s">
@@ -20267,10 +20659,10 @@
       <c r="AE97" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF97" s="4" t="s">
+      <c r="AF97" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="AG97" s="4" t="s">
+      <c r="AG97" s="13" t="s">
         <v>190</v>
       </c>
       <c r="AH97" s="2" t="s">
@@ -20288,7 +20680,7 @@
       <c r="AL97" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="AM97" s="2">
+      <c r="AM97" s="8">
         <v>5</v>
       </c>
       <c r="AN97" s="2" t="s">
@@ -20326,6 +20718,10 @@
       <c r="F98" s="3" t="s">
         <v>176</v>
       </c>
+      <c r="G98" s="8"/>
+      <c r="H98" s="11"/>
+      <c r="I98" s="11"/>
+      <c r="J98" s="11"/>
       <c r="K98" s="2" t="s">
         <v>175</v>
       </c>
@@ -20356,16 +20752,16 @@
       <c r="V98" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="W98" s="2" t="s">
+      <c r="W98" s="8" t="s">
         <v>169</v>
       </c>
       <c r="X98" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y98" s="2" t="s">
+      <c r="Y98" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="Z98" s="2" t="s">
+      <c r="Z98" s="8" t="s">
         <v>166</v>
       </c>
       <c r="AA98" s="4" t="s">
@@ -20383,10 +20779,10 @@
       <c r="AE98" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AF98" s="4" t="s">
+      <c r="AF98" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="AG98" s="4" t="s">
+      <c r="AG98" s="13" t="s">
         <v>160</v>
       </c>
       <c r="AH98" s="2" t="s">
@@ -20404,7 +20800,7 @@
       <c r="AL98" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="AM98" s="2" t="s">
+      <c r="AM98" s="8" t="s">
         <v>135</v>
       </c>
       <c r="AN98" s="2" t="s">
@@ -20442,6 +20838,10 @@
       <c r="F99" s="3" t="s">
         <v>145</v>
       </c>
+      <c r="G99" s="8"/>
+      <c r="H99" s="11"/>
+      <c r="I99" s="11"/>
+      <c r="J99" s="11"/>
       <c r="K99" s="2" t="s">
         <v>144</v>
       </c>
@@ -20472,16 +20872,16 @@
       <c r="V99" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="W99" s="2" t="s">
+      <c r="W99" s="8" t="s">
         <v>134</v>
       </c>
       <c r="X99" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y99" s="2" t="s">
+      <c r="Y99" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="Z99" s="2" t="s">
+      <c r="Z99" s="8" t="s">
         <v>132</v>
       </c>
       <c r="AA99" s="4" t="s">
@@ -20499,10 +20899,10 @@
       <c r="AE99" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="AF99" s="4" t="s">
+      <c r="AF99" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="AG99" s="4" t="s">
+      <c r="AG99" s="13" t="s">
         <v>58</v>
       </c>
       <c r="AH99" s="2" t="s">
@@ -20520,7 +20920,7 @@
       <c r="AL99" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="AM99" s="2" t="s">
+      <c r="AM99" s="8" t="s">
         <v>122</v>
       </c>
       <c r="AN99" s="2" t="s">
@@ -20558,6 +20958,10 @@
       <c r="F100" s="3" t="s">
         <v>111</v>
       </c>
+      <c r="G100" s="8"/>
+      <c r="H100" s="11"/>
+      <c r="I100" s="11"/>
+      <c r="J100" s="11"/>
       <c r="K100" s="2" t="s">
         <v>76</v>
       </c>
@@ -20588,16 +20992,16 @@
       <c r="V100" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="W100" s="2" t="s">
+      <c r="W100" s="8" t="s">
         <v>101</v>
       </c>
       <c r="X100" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y100" s="2" t="s">
+      <c r="Y100" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="Z100" s="2" t="s">
+      <c r="Z100" s="8" t="s">
         <v>99</v>
       </c>
       <c r="AA100" s="4" t="s">
@@ -20615,10 +21019,10 @@
       <c r="AE100" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="AF100" s="4" t="s">
+      <c r="AF100" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="AG100" s="4" t="s">
+      <c r="AG100" s="13" t="s">
         <v>93</v>
       </c>
       <c r="AH100" s="2" t="s">
@@ -20636,7 +21040,7 @@
       <c r="AL100" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="AM100" s="2" t="s">
+      <c r="AM100" s="8" t="s">
         <v>88</v>
       </c>
       <c r="AN100" s="2" t="s">
@@ -20674,6 +21078,10 @@
       <c r="F101" s="3" t="s">
         <v>77</v>
       </c>
+      <c r="G101" s="8"/>
+      <c r="H101" s="11"/>
+      <c r="I101" s="11"/>
+      <c r="J101" s="11"/>
       <c r="K101" s="2" t="s">
         <v>76</v>
       </c>
@@ -20704,16 +21112,16 @@
       <c r="V101" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="W101" s="2" t="s">
+      <c r="W101" s="8" t="s">
         <v>66</v>
       </c>
       <c r="X101" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y101" s="2" t="s">
+      <c r="Y101" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="Z101" s="2" t="s">
+      <c r="Z101" s="8" t="s">
         <v>63</v>
       </c>
       <c r="AA101" s="4" t="s">
@@ -20731,10 +21139,10 @@
       <c r="AE101" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AF101" s="4" t="s">
+      <c r="AF101" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="AG101" s="4" t="s">
+      <c r="AG101" s="13" t="s">
         <v>57</v>
       </c>
       <c r="AH101" s="2" t="s">
@@ -20752,7 +21160,7 @@
       <c r="AL101" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AM101" s="2" t="s">
+      <c r="AM101" s="8" t="s">
         <v>52</v>
       </c>
       <c r="AN101" s="2" t="s">

--- a/apps/api/data/excel_templates/countries.xlsx
+++ b/apps/api/data/excel_templates/countries.xlsx
@@ -19806,7 +19806,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <autoFilter ref="A1:AS1"/>
   <conditionalFormatting sqref="G2:G101">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">

--- a/apps/api/data/excel_templates/countries.xlsx
+++ b/apps/api/data/excel_templates/countries.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection lockStructure="1"/>
+  <workbookProtection workbookPassword="DB2D" lockStructure="1"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -713,7 +713,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DB2D"/>
   <autoFilter ref="A1:AS1"/>
   <dataValidations count="14">
     <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">

--- a/apps/api/data/excel_templates/countries.xlsx
+++ b/apps/api/data/excel_templates/countries.xlsx
@@ -740,12 +740,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Vietnamese (official)</t>
+          <t>VIETNAMESE</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Hungarian (official)</t>
+          <t>HUNGARIAN</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Belarusian, Russian (both official)</t>
+          <t>BELARUSIAN;RUSSIAN</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>German (official), English widely spoken</t>
+          <t>GERMAN;ENGLISH</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Persian (Farsi, official), Kurdish, Azeri</t>
+          <t>PERSIAN;KURDISH;AZERBAIJANI</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Turkish (official)</t>
+          <t>TURKISH</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>German (official), English widely spoken</t>
+          <t>GERMAN;ENGLISH</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>German, French, Italian, Romansh (all official)</t>
+          <t>GERMAN;FRENCH;ITALIAN;ROMANSH</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>English (official), Guyanese Creole</t>
+          <t>ENGLISH;GUYANESE_CREOLE</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -2315,12 +2315,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Catalan (official), Spanish, French, Portuguese</t>
+          <t>CATALAN;SPANISH;FRENCH;PORTUGUESE</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Medium to High</t>
+          <t>MEDIUM_HIGH</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Thai (official)</t>
+          <t>THAI</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2665,12 +2665,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Cantonese (official), English (official)</t>
+          <t>CHINESE_CANTONESE;ENGLISH</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Serbian (official)</t>
+          <t>SERBIAN</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -3013,14 +3013,9 @@
           <t>7 million (Foreign Born: ~200,000)</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Spanish and Guarani (both official)</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -3074,7 +3069,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -3190,12 +3185,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Cantonese, Portuguese (official)</t>
+          <t>CHINESE_CANTONESE;PORTUGUESE</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -3249,7 +3244,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -3365,12 +3360,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>French (official), regional languages</t>
+          <t>FRENCH</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -3424,7 +3419,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -3540,12 +3535,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>English (official)</t>
+          <t>ENGLISH</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -3599,7 +3594,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3715,12 +3710,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Luxembourgish, French, German</t>
+          <t>LUXEMBOURGISH;FRENCH;GERMAN</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -3774,7 +3769,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3890,12 +3885,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Montenegrin (official), Serbian, Bosnian</t>
+          <t>MONTENEGRIN;SERBIAN;BOSNIAN</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -3949,7 +3944,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -4065,12 +4060,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Italian (official), regional dialects</t>
+          <t>ITALIAN</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -4124,7 +4119,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -4240,12 +4235,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>11 official languages including Zulu, Xhosa, English</t>
+          <t>XHOSA;ENGLISH</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -4299,7 +4294,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -4415,12 +4410,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Arabic (official), French, English</t>
+          <t>ARABIC;FRENCH;ENGLISH</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -4474,7 +4469,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -4590,12 +4585,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Bulgarian (official), Turkish, Romani</t>
+          <t>BULGARIAN;TURKISH;ROMANI</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -4649,7 +4644,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -4765,12 +4760,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>English (official)</t>
+          <t>ENGLISH</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -4824,7 +4819,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4940,12 +4935,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Dhivehi (official), English widely spoken</t>
+          <t>DHIVEHI;ENGLISH</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -4999,7 +4994,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>Medium to High</t>
+          <t>MEDIUM_HIGH</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -5115,12 +5110,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Maltese, English (both official)</t>
+          <t>MALTESE;ENGLISH</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -5174,7 +5169,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -5290,12 +5285,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Korean (official)</t>
+          <t>KOREAN</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -5349,7 +5344,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -5465,12 +5460,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Spanish (official), some indigenous languages</t>
+          <t>SPANISH</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -5524,7 +5519,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -5640,12 +5635,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Danish (official), English widely spoken</t>
+          <t>DANISH;ENGLISH</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -5699,7 +5694,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -5815,12 +5810,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>English, Malay, Mandarin, Tamil (all official)</t>
+          <t>ENGLISH;MALAY;CHINESE_MANDARIN;TAMIL</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -5874,7 +5869,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -5990,12 +5985,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Finnish, Swedish (both official)</t>
+          <t>FINNISH;SWEDISH</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -6049,7 +6044,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -6165,12 +6160,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Norwegian (Bokmål and Nynorsk)</t>
+          <t>NORWEGIAN</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -6224,7 +6219,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -6340,12 +6335,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Slovak (official)</t>
+          <t>SLOVAK</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -6399,7 +6394,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -6515,12 +6510,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Arabic (official), English widely spoken</t>
+          <t>ARABIC;ENGLISH</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -6574,7 +6569,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -6690,12 +6685,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Spanish (official), English widely spoken</t>
+          <t>SPANISH;ENGLISH</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -6749,7 +6744,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -6840,52 +6835,52 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CON-000036</t>
+          <t>CON-000045</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Wellington</t>
+          <t>Panama City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>5.1 million (Foreign Born: ~1.3 million)</t>
+          <t>4.4 million (Foreign Born: ~800,000)</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>English, Māori, New Zealand Sign Language (official)</t>
+          <t>SPANISH;ENGLISH</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>5°C to 30°C</t>
+          <t>22°C to 34°C</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Temperate; mild, wet winters and warm summers</t>
+          <t>Tropical; hot and humid year-round</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -6895,41 +6890,41 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Excellent; strong emphasis on outdoor life and balanced work culture</t>
+          <t>Varies; urban more fast-paced, rural slower</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>Agriculture, Forestry, Tourism, Manufacturing, Services</t>
+          <t>Banking, Logistics, Shipping, Tourism</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>150+</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>NZD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="W37" t="n">
-        <v>68000</v>
+        <v>12000</v>
       </c>
       <c r="X37" t="n">
-        <v>770000</v>
+        <v>120000</v>
       </c>
       <c r="Y37" t="n">
-        <v>1900</v>
+        <v>600</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>Medium to High</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Known for stunning nature and Maori culture</t>
+          <t>Famous for Panama Canal and biodiversity</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -6939,123 +6934,123 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Relatively easy; skilled migration points system</t>
+          <t>Moderate difficulty; easier for skilled and business workers</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>Highly globalized</t>
+          <t>Moderately globalized</t>
         </is>
       </c>
       <c r="AF37" t="n">
-        <v>45000</v>
+        <v>10000</v>
       </c>
       <c r="AG37" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>10.5–39% (progressive)</t>
+          <t>0–25% (progressive)</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>~4 million</t>
+          <t>~3 million</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Very Good</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>30% Bachelor's, 10% Master's, 2% PhD</t>
+          <t>20% Bachelor's, 6% Master's, 1% PhD</t>
         </is>
       </c>
       <c r="AM37" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>University of Auckland, Victoria University of Wellington, University of Otago</t>
+          <t>University of Panama, Technological University of Panama</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>European descent, Māori, others</t>
+          <t>Mestizo, Indigenous, Afro-Panamanian</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>Christianity (mostly), Māori spiritual beliefs</t>
+          <t>Christianity (mostly Catholic)</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>Respect for nature, community, egalitarianism</t>
+          <t>Family, community, resilience</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>New Zealanders (Kiwis) are friendly, outdoorsy, and proud of their indigenous Māori heritage and natural environment.</t>
+          <t>Panamanians are warm, community-oriented, and proud of their diverse cultural heritage.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CON-000037</t>
+          <t>CON-000036</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Dublin</t>
+          <t>Wellington</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>5 million (Foreign Born: ~1 million)</t>
+          <t>5.1 million (Foreign Born: ~1.3 million)</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>English, Irish (both official)</t>
+          <t>ENGLISH;MAORI</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0°C to 25°C</t>
+          <t>5°C to 30°C</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Temperate maritime; mild, wet winters and summers</t>
+          <t>Temperate; mild, wet winters and warm summers</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -7070,41 +7065,41 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Excellent; good work-life balance, emphasis on family time</t>
+          <t>Excellent; strong emphasis on outdoor life and balanced work culture</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>Pharmaceuticals, Finance, Technology, Medical Devices</t>
+          <t>Agriculture, Forestry, Tourism, Manufacturing, Services</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>350+</t>
+          <t>150+</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>NZD</t>
         </is>
       </c>
       <c r="W38" t="n">
-        <v>55000</v>
+        <v>68000</v>
       </c>
       <c r="X38" t="n">
-        <v>350000</v>
+        <v>770000</v>
       </c>
       <c r="Y38" t="n">
-        <v>1200</v>
+        <v>1900</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>MEDIUM_HIGH</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Known for tech sector and green landscapes</t>
+          <t>Known for stunning nature and Maori culture</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -7114,12 +7109,12 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Relatively easy; EU nationals have easier access</t>
+          <t>Relatively easy; skilled migration points system</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
@@ -7128,134 +7123,134 @@
         </is>
       </c>
       <c r="AF38" t="n">
-        <v>35000</v>
+        <v>45000</v>
       </c>
       <c r="AG38" t="n">
-        <v>7000</v>
+        <v>3000</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>20–40% (progressive)</t>
+          <t>10.5–39% (progressive)</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>~10 million</t>
+          <t>~4 million</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Very Good</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>35% Bachelor's, 12% Master's, 2% PhD</t>
+          <t>30% Bachelor's, 10% Master's, 2% PhD</t>
         </is>
       </c>
       <c r="AM38" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>Trinity College Dublin, University College Dublin, University of Limerick</t>
+          <t>University of Auckland, Victoria University of Wellington, University of Otago</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Irish, British, others</t>
+          <t>European descent, Māori, others</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>Christianity (mostly Catholic)</t>
+          <t>Christianity (mostly), Māori spiritual beliefs</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>Hospitality, community, wit, respect for history</t>
+          <t>Respect for nature, community, egalitarianism</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>Irish people are friendly, humorous, and community-minded with strong cultural pride and traditions.</t>
+          <t>New Zealanders (Kiwis) are friendly, outdoorsy, and proud of their indigenous Māori heritage and natural environment.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CON-000038</t>
+          <t>CON-000037</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Dublin</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>47 million (Foreign Born: ~7 million)</t>
+          <t>5 million (Foreign Born: ~1 million)</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Spanish (official), regional languages</t>
+          <t>ENGLISH;IRISH</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0°C to 40°C</t>
+          <t>0°C to 25°C</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mediterranean; hot summers, mild winters</t>
+          <t>Temperate maritime; mild, wet winters and summers</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Good; emphasis on leisure and social life</t>
+          <t>Excellent; good work-life balance, emphasis on family time</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>Tourism, Automotive, Agriculture, Energy, Textiles</t>
+          <t>Pharmaceuticals, Finance, Technology, Medical Devices</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>150+</t>
+          <t>350+</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -7264,37 +7259,37 @@
         </is>
       </c>
       <c r="W39" t="n">
-        <v>25000</v>
+        <v>55000</v>
       </c>
       <c r="X39" t="n">
-        <v>220000</v>
+        <v>350000</v>
       </c>
       <c r="Y39" t="n">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>Medium to High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Known for art, festivals, and cuisine</t>
+          <t>Known for tech sector and green landscapes</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Requires 10 years of residency</t>
+          <t>Requires 5 years of residency</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Moderate difficulty; easier for EU nationals</t>
+          <t>Relatively easy; EU nationals have easier access</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr">
@@ -7303,47 +7298,47 @@
         </is>
       </c>
       <c r="AF39" t="n">
-        <v>80000</v>
+        <v>35000</v>
       </c>
       <c r="AG39" t="n">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>19–47% (progressive)</t>
+          <t>20–40% (progressive)</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>~83 million</t>
+          <t>~10 million</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>40+</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Excellent</t>
         </is>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>30% Bachelor's, 10% Master's, 2% PhD</t>
+          <t>35% Bachelor's, 12% Master's, 2% PhD</t>
         </is>
       </c>
       <c r="AM39" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>University of Barcelona, Complutense University of Madrid, University of Valencia</t>
+          <t>Trinity College Dublin, University College Dublin, University of Limerick</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Irish, British, others</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
@@ -7353,59 +7348,59 @@
       </c>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>Family, tradition, enjoyment of life</t>
+          <t>Hospitality, community, wit, respect for history</t>
         </is>
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>Spaniards are warm, family-oriented, and known for their relaxed lifestyle and cultural festivals.</t>
+          <t>Irish people are friendly, humorous, and community-minded with strong cultural pride and traditions.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CON-000039</t>
+          <t>CON-000038</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>46 million (Foreign Born: ~2.3 million)</t>
+          <t>47 million (Foreign Born: ~7 million)</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Spanish (official), English commonly taught</t>
+          <t>SPANISH</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Medium to High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>-5°C to 35°C</t>
+          <t>0°C to 40°C</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Subtropical in north, temperate in center, cold in south</t>
+          <t>Mediterranean; hot summers, mild winters</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -7420,192 +7415,192 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Improving; urban areas favor work-life balance, especially in public sector</t>
+          <t>Good; emphasis on leisure and social life</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>Agriculture, Automotive, Food Processing, Energy</t>
+          <t>Tourism, Automotive, Agriculture, Energy, Textiles</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>150+</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="W40" t="n">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="X40" t="n">
-        <v>70000</v>
+        <v>220000</v>
       </c>
       <c r="Y40" t="n">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>MEDIUM_HIGH</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Famous for tango and beef exports</t>
+          <t>Known for art, festivals, and cuisine</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Requires 2 years of residency</t>
+          <t>Requires 10 years of residency</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Moderate difficulty; special permits for skilled labor</t>
+          <t>Moderate difficulty; easier for EU nationals</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>Moderately globalized</t>
+          <t>Highly globalized</t>
         </is>
       </c>
       <c r="AF40" t="n">
-        <v>10000</v>
+        <v>80000</v>
       </c>
       <c r="AG40" t="n">
-        <v>1200</v>
+        <v>6000</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>5–35% progressive</t>
+          <t>19–47% (progressive)</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>~7 million</t>
+          <t>~83 million</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>35+</t>
+          <t>40+</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>20% Bachelor’s, 7% Master’s, 1% PhD</t>
+          <t>30% Bachelor's, 10% Master's, 2% PhD</t>
         </is>
       </c>
       <c r="AM40" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>University of Buenos Aires, National University of La Plata</t>
+          <t>University of Barcelona, Complutense University of Madrid, University of Valencia</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Argentines, Italians, Spanish</t>
+          <t>Spanish</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>Christianity (mostly Catholic), some Jewish and Muslim populations</t>
+          <t>Christianity (mostly Catholic)</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
         <is>
-          <t>Family loyalty, social equality, pride in culture and history</t>
+          <t>Family, tradition, enjoyment of life</t>
         </is>
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>Argentinians are warm, expressive, and socially connected, with a passion for community and conversation.</t>
+          <t>Spaniards are warm, family-oriented, and known for their relaxed lifestyle and cultural festivals.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BN</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Brunei</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CON-000040</t>
+          <t>CON-000039</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Bandar Seri Begawan</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>450,000 (Foreign Born: ~150,000)</t>
+          <t>46 million (Foreign Born: ~2.3 million)</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Malay (official), English widely used</t>
+          <t>SPANISH;ENGLISH</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>MEDIUM_HIGH</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>23°C to 32°C</t>
+          <t>-5°C to 35°C</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Equatorial; hot, humid, heavy rainfall year-round</t>
+          <t>Subtropical in north, temperate in center, cold in south</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Very low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Low to moderate</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Strong in public sector; shorter workweeks and family-focused</t>
+          <t>Improving; urban areas favor work-life balance, especially in public sector</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>Oil and Gas, Petrochemicals, Banking, Halal Food, Islamic Finance</t>
+          <t>Agriculture, Automotive, Food Processing, Energy</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>~15</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -7614,37 +7609,37 @@
         </is>
       </c>
       <c r="W41" t="n">
-        <v>28000</v>
+        <v>10000</v>
       </c>
       <c r="X41" t="n">
-        <v>180000</v>
+        <v>70000</v>
       </c>
       <c r="Y41" t="n">
-        <v>800</v>
+        <v>350</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>Medium to High</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>Known for wealth from oil and gas production</t>
+          <t>Famous for tango and beef exports</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Requires 10 years of residency</t>
+          <t>Requires 2 years of residency</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Difficult; work permits restricted</t>
+          <t>Moderate difficulty; special permits for skilled labor</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr">
@@ -7653,109 +7648,109 @@
         </is>
       </c>
       <c r="AF41" t="n">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="AG41" t="n">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>No income tax</t>
+          <t>5–35% progressive</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>~0.3 million</t>
+          <t>~7 million</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>35+</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>35% Bachelor's, 10% Master's, 1% PhD</t>
+          <t>20% Bachelor’s, 7% Master’s, 1% PhD</t>
         </is>
       </c>
       <c r="AM41" t="n">
-        <v>5</v>
+        <v>130</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>Universiti Brunei Darussalam, Universiti Teknologi Brunei</t>
+          <t>University of Buenos Aires, National University of La Plata</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Malays, Chinese, Indigenous, Expats</t>
+          <t>Argentines, Italians, Spanish</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>Islam (official), Buddhism, Christianity</t>
+          <t>Christianity (mostly Catholic), some Jewish and Muslim populations</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>Islamic values, respect for hierarchy, modesty, harmony</t>
+          <t>Family loyalty, social equality, pride in culture and history</t>
         </is>
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>Bruneians are polite, respectful, and guided by Islamic and traditional values.</t>
+          <t>Argentinians are warm, expressive, and socially connected, with a passion for community and conversation.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>BN</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>American Samoa</t>
+          <t>Brunei</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CON-000041</t>
+          <t>CON-000040</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Pago Pago</t>
+          <t>Bandar Seri Begawan</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>45,000 (Foreign Born: ~8,000)</t>
+          <t>450,000 (Foreign Born: ~150,000)</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Samoan (official), English</t>
+          <t>MALAY;ENGLISH</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>24°C to 30°C</t>
+          <t>23°C to 32°C</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tropical, humid, with abundant rainfall year-round</t>
+          <t>Equatorial; hot, humid, heavy rainfall year-round</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -7765,22 +7760,22 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Low to moderate</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Generally good; life is slower-paced and family-oriented</t>
+          <t>Strong in public sector; shorter workweeks and family-focused</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>Tuna fishing, Government services, Tourism, Agriculture</t>
+          <t>Oil and Gas, Petrochemicals, Banking, Halal Food, Islamic Finance</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>Few</t>
+          <t>~15</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -7789,420 +7784,420 @@
         </is>
       </c>
       <c r="W42" t="n">
-        <v>15000</v>
+        <v>28000</v>
       </c>
       <c r="X42" t="n">
-        <v>120000</v>
+        <v>180000</v>
       </c>
       <c r="Y42" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM_HIGH</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>Known for its unique Polynesian culture</t>
+          <t>Known for wealth from oil and gas production</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>US territory rules apply</t>
+          <t>Requires 10 years of residency</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>US work permit rules apply</t>
+          <t>Difficult; work permits restricted</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>Not ranked</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>Low globalization</t>
+          <t>Moderately globalized</t>
         </is>
       </c>
       <c r="AF42" t="n">
-        <v>100</v>
+        <v>500</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>200</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>US federal tax system applies</t>
+          <t>No income tax</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>~50,000</t>
+          <t>~0.3 million</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>20% Bachelor’s, 5% Master’s, &lt;1% PhD</t>
+          <t>35% Bachelor's, 10% Master's, 1% PhD</t>
         </is>
       </c>
       <c r="AM42" t="n">
-        <v>45659</v>
+        <v>5</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>American Samoa Community College</t>
+          <t>Universiti Brunei Darussalam, Universiti Teknologi Brunei</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Samoans, Tongans, other Pacific Islanders</t>
+          <t>Malays, Chinese, Indigenous, Expats</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>Christianity (overwhelmingly Protestant and Catholic)</t>
+          <t>Islam (official), Buddhism, Christianity</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>Respect for family (aiga), elders, tradition (fa'a Samoa)</t>
+          <t>Islamic values, respect for hierarchy, modesty, harmony</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>Samoans are community-focused, respectful, and maintain strong traditional customs and values.</t>
+          <t>Bruneians are polite, respectful, and guided by Islamic and traditional values.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DZ</t>
+          <t>AS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>American Samoa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CON-000042</t>
+          <t>CON-000041</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Algiers</t>
+          <t>Pago Pago</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>45 million (Foreign Born: ~250,000)</t>
+          <t>45,000 (Foreign Born: ~8,000)</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Arabic (official), Berber, French (widely spoken)</t>
+          <t>SAMOAN;ENGLISH</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>24°C to 30°C</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Tropical, humid, with abundant rainfall year-round</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Very low</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Generally good; life is slower-paced and family-oriented</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Tuna fishing, Government services, Tourism, Agriculture</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Few</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="W43" t="n">
+        <v>15000</v>
+      </c>
+      <c r="X43" t="n">
+        <v>120000</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>700</v>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Known for its unique Polynesian culture</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>US territory rules apply</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>US work permit rules apply</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>Not ranked</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>Low globalization</t>
+        </is>
+      </c>
+      <c r="AF43" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>US federal tax system applies</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>~50,000</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>5°C to 35°C</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Arid to semi-arid; hot, dry summers and mild, wetter winters</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>Relatively high</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>Work-centered culture; improving balance in urban areas</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Oil &amp; Gas, Petrochemicals, Agriculture, Mining</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Few</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="W43" t="n">
-        <v>7000</v>
-      </c>
-      <c r="X43" t="n">
-        <v>50000</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>250</v>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>Low to Medium</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>Largest country in Africa by land area</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>Requires 10 years of residency</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Moderate difficulty, work permits granted selectively</t>
-        </is>
-      </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>Low to moderately globalized</t>
-        </is>
-      </c>
-      <c r="AF43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>400</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>0–35% progressive</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>~2 million</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>20+</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>15% Bachelor’s, 4% Master’s, &lt;1% PhD</t>
+          <t>20% Bachelor’s, 5% Master’s, &lt;1% PhD</t>
         </is>
       </c>
       <c r="AM43" t="n">
-        <v>50</v>
+        <v>45659</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>University of Algiers, Constantine 1 University</t>
+          <t>American Samoa Community College</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Algerians, Berbers</t>
+          <t>Samoans, Tongans, other Pacific Islanders</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>Islam (Sunni majority)</t>
+          <t>Christianity (overwhelmingly Protestant and Catholic)</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>Respect for elders, hospitality, religious devotion</t>
+          <t>Respect for family (aiga), elders, tradition (fa'a Samoa)</t>
         </is>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>Algerians are proud, community-oriented, and deeply rooted in religious and family traditions.</t>
+          <t>Samoans are community-focused, respectful, and maintain strong traditional customs and values.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>UA</t>
+          <t>DZ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CON-000043</t>
+          <t>CON-000042</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Algiers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>44 million (Foreign Born: ~500,000)</t>
+          <t>45 million (Foreign Born: ~250,000)</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Ukrainian (official), Russian widely spoken</t>
+          <t>ARABIC;BERBER;FRENCH</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>5°C to 35°C</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Arid to semi-arid; hot, dry summers and mild, wetter winters</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Relatively high</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Work-centered culture; improving balance in urban areas</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas, Petrochemicals, Agriculture, Mining</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Few</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="W44" t="n">
+        <v>7000</v>
+      </c>
+      <c r="X44" t="n">
+        <v>50000</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>250</v>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>LOW_MEDIUM</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>Largest country in Africa by land area</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>Requires 10 years of residency</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Moderate difficulty, work permits granted selectively</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>Low to moderately globalized</t>
+        </is>
+      </c>
+      <c r="AF44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>400</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>0–35% progressive</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>~2 million</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>20+</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>-20°C to 30°C</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Continental; cold winters, warm summers</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>Developing; improving work-life balance</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Agriculture, Metallurgy, IT, Manufacturing</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Few</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="W44" t="n">
-        <v>5000</v>
-      </c>
-      <c r="X44" t="n">
-        <v>30000</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>200</v>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>Famous for fertile plains and historic cities</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>Requires 5 years of residency</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Moderate difficulty; easier for skilled workers</t>
-        </is>
-      </c>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>Moderately globalized</t>
-        </is>
-      </c>
-      <c r="AF44" t="n">
-        <v>15000</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>18% flat</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>~14 million</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>30+</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>15% Bachelor's, 5% Master's, &lt;1% PhD</t>
+          <t>15% Bachelor’s, 4% Master’s, &lt;1% PhD</t>
         </is>
       </c>
       <c r="AM44" t="n">
@@ -8210,79 +8205,79 @@
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>Taras Shevchenko National University, National Technical University of Ukraine</t>
+          <t>University of Algiers, Constantine 1 University</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Ukrainian</t>
+          <t>Algerians, Berbers</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>Christianity (mostly Orthodox)</t>
+          <t>Islam (Sunni majority)</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>Resilience, family, tradition</t>
+          <t>Respect for elders, hospitality, religious devotion</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>Ukrainians are known for their resilience, strong cultural identity, and community spirit.</t>
+          <t>Algerians are proud, community-oriented, and deeply rooted in religious and family traditions.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>UA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Bahamas</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CON-000044</t>
+          <t>CON-000043</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Nassau</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>400,000 (Foreign Born: ~50,000)</t>
+          <t>44 million (Foreign Born: ~500,000)</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>English (official)</t>
+          <t>UKRAINIAN;RUSSIAN</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>20°C to 32°C</t>
+          <t>-20°C to 30°C</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tropical; warm year-round</t>
+          <t>Continental; cold winters, warm summers</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -8292,12 +8287,12 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Good; relaxed island lifestyle</t>
+          <t>Developing; improving work-life balance</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>Tourism, Financial Services, Shipping</t>
+          <t>Agriculture, Metallurgy, IT, Manufacturing</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -8307,67 +8302,67 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="W45" t="n">
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="X45" t="n">
-        <v>350000</v>
+        <v>30000</v>
       </c>
       <c r="Y45" t="n">
+        <v>200</v>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>Famous for fertile plains and historic cities</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>Requires 5 years of residency</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Moderate difficulty; easier for skilled workers</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>Moderately globalized</t>
+        </is>
+      </c>
+      <c r="AF45" t="n">
+        <v>15000</v>
+      </c>
+      <c r="AG45" t="n">
         <v>1000</v>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>Known for coral reefs and tourism</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>Requires 10 years of residency</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Moderate difficulty; easier in tourism sector</t>
-        </is>
-      </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>Moderately globalized</t>
-        </is>
-      </c>
-      <c r="AF45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>300</v>
-      </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>No personal income tax</t>
+          <t>18% flat</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>~7 million</t>
+          <t>~14 million</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -8377,210 +8372,210 @@
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>25% Bachelor's, 7% Master's, 1% PhD</t>
+          <t>15% Bachelor's, 5% Master's, &lt;1% PhD</t>
         </is>
       </c>
       <c r="AM45" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>University of The Bahamas</t>
+          <t>Taras Shevchenko National University, National Technical University of Ukraine</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Afro-Bahamian</t>
+          <t>Ukrainian</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>Christianity (mostly Protestant)</t>
+          <t>Christianity (mostly Orthodox)</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>Hospitality, community, relaxation</t>
+          <t>Resilience, family, tradition</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>Bahamians are known for their warm hospitality, community spirit, and relaxed island lifestyle.</t>
+          <t>Ukrainians are known for their resilience, strong cultural identity, and community spirit.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>The Bahamas</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CON-000045</t>
+          <t>CON-000044</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Panama City</t>
+          <t>Nassau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>4.4 million (Foreign Born: ~800,000)</t>
+          <t>400,000 (Foreign Born: ~50,000)</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Spanish (official), English widely spoken</t>
+          <t>ENGLISH</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>22°C to 34°C</t>
+          <t>20°C to 32°C</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tropical; hot and humid year-round</t>
+          <t>Tropical; warm year-round</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Good; relaxed island lifestyle</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Tourism, Financial Services, Shipping</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Few</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="W46" t="n">
+        <v>25000</v>
+      </c>
+      <c r="X46" t="n">
+        <v>350000</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Known for coral reefs and tourism</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Requires 10 years of residency</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Moderate difficulty; easier in tourism sector</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>Moderately globalized</t>
+        </is>
+      </c>
+      <c r="AF46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>300</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>No personal income tax</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>~7 million</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>Varies; urban more fast-paced, rural slower</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Banking, Logistics, Shipping, Tourism</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>30+</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="W46" t="n">
-        <v>12000</v>
-      </c>
-      <c r="X46" t="n">
-        <v>120000</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>600</v>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>Famous for Panama Canal and biodiversity</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>Requires 5 years of residency</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Moderate difficulty; easier for skilled and business workers</t>
-        </is>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>Moderately globalized</t>
-        </is>
-      </c>
-      <c r="AF46" t="n">
-        <v>10000</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>0–25% (progressive)</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>~3 million</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>20% Bachelor's, 6% Master's, 1% PhD</t>
+          <t>25% Bachelor's, 7% Master's, 1% PhD</t>
         </is>
       </c>
       <c r="AM46" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>University of Panama, Technological University of Panama</t>
+          <t>University of The Bahamas</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Mestizo, Indigenous, Afro-Panamanian</t>
+          <t>Afro-Bahamian</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>Christianity (mostly Catholic)</t>
+          <t>Christianity (mostly Protestant)</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>Family, community, resilience</t>
+          <t>Hospitality, community, relaxation</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>Panamanians are warm, community-oriented, and proud of their diverse cultural heritage.</t>
+          <t>Bahamians are known for their warm hospitality, community spirit, and relaxed island lifestyle.</t>
         </is>
       </c>
     </row>
@@ -8612,12 +8607,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Arabic (official), English widely spoken</t>
+          <t>ARABIC;ENGLISH</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -8671,7 +8666,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -8787,12 +8782,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>French (official)</t>
+          <t>FRENCH</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -8846,7 +8841,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -8962,12 +8957,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>English, French (both official), many immigrant languages</t>
+          <t>ENGLISH;FRENCH</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Very high</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -9021,7 +9016,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -9137,12 +9132,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Icelandic (official), English widely spoken</t>
+          <t>ICELANDIC;ENGLISH</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -9196,7 +9191,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -9312,12 +9307,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Arabic (official), Berber languages, French</t>
+          <t>ARABIC;BERBER;FRENCH</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -9371,7 +9366,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -9487,12 +9482,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Portuguese (official), Umbundu, Kimbundu</t>
+          <t>PORTUGUESE;UMBUNDU;KIMBUNDU</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -9546,7 +9541,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -9662,12 +9657,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Arabic (official)</t>
+          <t>ARABIC</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -9721,7 +9716,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>Medium to High</t>
+          <t>MEDIUM_HIGH</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -9837,12 +9832,12 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Malay, Mandarin, English, Tamil</t>
+          <t>MALAY;CHINESE_MANDARIN;ENGLISH;TAMIL</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -9896,7 +9891,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -10012,12 +10007,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Italian (official)</t>
+          <t>ITALIAN</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -10071,7 +10066,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -10187,12 +10182,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>English (de facto)</t>
+          <t>ENGLISH</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -10246,7 +10241,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -10362,12 +10357,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Spanish (official), Quechua, Aymara</t>
+          <t>SPANISH;QUECHUA;AYMARA</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -10421,7 +10416,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -10537,12 +10532,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Croatian (official), English widely spoken</t>
+          <t>CROATIAN;ENGLISH</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -10596,7 +10591,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -10712,12 +10707,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Georgian (official), Russian, Armenian</t>
+          <t>GEORGIAN;RUSSIAN;ARMENIAN</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -10771,7 +10766,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -10887,12 +10882,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Spanish (official)</t>
+          <t>SPANISH</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -10946,7 +10941,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -11062,12 +11057,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Spanish, English (both official)</t>
+          <t>SPANISH;ENGLISH</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -11121,7 +11116,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>Medium to High</t>
+          <t>MEDIUM_HIGH</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -11237,12 +11232,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Bosnian, Croatian, Serbian</t>
+          <t>BOSNIAN;CROATIAN;SERBIAN</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -11296,7 +11291,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -11412,12 +11407,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Arabic (official), English widely spoken</t>
+          <t>ARABIC;ENGLISH</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -11471,7 +11466,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -11587,12 +11582,12 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>English (official), Bajan Creole</t>
+          <t>ENGLISH;BAJAN_CREOLE</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -11646,7 +11641,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>Medium to High</t>
+          <t>MEDIUM_HIGH</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -11762,12 +11757,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Indonesian (official), local languages</t>
+          <t>INDONESIAN</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -11821,7 +11816,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -11937,12 +11932,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>English (official), various immigrant languages</t>
+          <t>ENGLISH</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -11996,7 +11991,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -12112,12 +12107,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Urdu (official), English, regional languages</t>
+          <t>URDU;ENGLISH</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -12171,7 +12166,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -12287,12 +12282,12 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Mandarin Chinese (official)</t>
+          <t>CHINESE_MANDARIN</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -12346,7 +12341,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -12462,12 +12457,12 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Portuguese (official), regional dialects</t>
+          <t>PORTUGUESE</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -12521,7 +12516,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -12637,12 +12632,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Albanian (official), Greek</t>
+          <t>ALBANIAN;GREEK</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -12696,7 +12691,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -12812,12 +12807,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Lithuanian (official), Russian, Polish</t>
+          <t>LITHUANIAN;RUSSIAN;POLISH</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -12871,7 +12866,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -12987,12 +12982,12 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Armenian (official), Russian widely spoken</t>
+          <t>ARMENIAN;RUSSIAN</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -13046,7 +13041,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -13162,12 +13157,12 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Romanian (official), Russian, Ukrainian</t>
+          <t>ROMANIAN;RUSSIAN;UKRAINIAN</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -13221,7 +13216,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -13337,12 +13332,12 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Macedonian (official), Albanian</t>
+          <t>MACEDONIAN;ALBANIAN</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -13396,7 +13391,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -13512,12 +13507,12 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Slovene (official)</t>
+          <t>SLOVENIAN</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -13571,7 +13566,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -13687,12 +13682,12 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Spanish (official), some indigenous languages</t>
+          <t>SPANISH</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -13746,7 +13741,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -13862,12 +13857,12 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Kazakh (official), Russian</t>
+          <t>KAZAKH;RUSSIAN</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -13921,7 +13916,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -14037,12 +14032,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Romanian (official)</t>
+          <t>ROMANIAN</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -14096,7 +14091,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -14212,12 +14207,12 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>English (official), French Creole</t>
+          <t>ENGLISH</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -14271,7 +14266,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -14387,12 +14382,12 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Spanish (official), Quechua, Shuar</t>
+          <t>SPANISH;QUECHUA;SHUAR</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -14446,7 +14441,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -14562,12 +14557,12 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>English, Chamorro (official)</t>
+          <t>ENGLISH;CHAMORRO</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -14621,7 +14616,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>Medium to High</t>
+          <t>MEDIUM_HIGH</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -14737,12 +14732,12 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Dutch (official), Frisian, English widely spoken</t>
+          <t>DUTCH;FRISIAN;ENGLISH</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -14796,7 +14791,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -14912,12 +14907,12 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Russian (official)</t>
+          <t>RUSSIAN</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -14971,7 +14966,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -15087,12 +15082,12 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Spanish (official), Indigenous languages</t>
+          <t>SPANISH</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -15146,7 +15141,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -15262,12 +15257,12 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Japanese (official)</t>
+          <t>JAPANESE</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -15321,7 +15316,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -15437,12 +15432,12 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Filipino, English (both official)</t>
+          <t>FILIPINO;ENGLISH</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -15496,7 +15491,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -15612,12 +15607,12 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Arabic (official), English, French</t>
+          <t>ARABIC;ENGLISH;FRENCH</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -15671,7 +15666,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -15787,12 +15782,12 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Dutch, French, German (all official), English widely spoken</t>
+          <t>DUTCH;FRENCH;GERMAN;ENGLISH</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Very high</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -15846,7 +15841,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -15962,12 +15957,12 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Spanish (official), Haitian Creole</t>
+          <t>SPANISH;HAITIAN_CREOLE</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -16021,7 +16016,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -16137,12 +16132,12 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Arabic (official), English widely spoken</t>
+          <t>ARABIC;ENGLISH</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -16196,7 +16191,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -16312,12 +16307,12 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Seychellois Creole, English, French (all official)</t>
+          <t>SEYCHELLOIS_CREOLE;ENGLISH;FRENCH</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -16371,7 +16366,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -16487,12 +16482,12 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Greek (official)</t>
+          <t>GREEK</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -16546,7 +16541,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -16662,12 +16657,12 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Czech (official), Slovak, minority languages</t>
+          <t>CZECH;SLOVAK</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -16721,7 +16716,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -16837,12 +16832,12 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Swedish (official)</t>
+          <t>SWEDISH</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -16896,7 +16891,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -17012,12 +17007,12 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Portuguese (official)</t>
+          <t>PORTUGUESE</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -17071,7 +17066,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -17187,12 +17182,12 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Arabic (official), English widely used</t>
+          <t>ARABIC;ENGLISH</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -17246,7 +17241,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>Medium to High</t>
+          <t>MEDIUM_HIGH</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -17362,12 +17357,12 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>English (official)</t>
+          <t>ENGLISH</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -17421,7 +17416,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -17537,12 +17532,12 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Hindi (official), English (associate), 21 other official languages</t>
+          <t>HINDI;ENGLISH</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -17596,7 +17591,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>Low to Medium</t>
+          <t>LOW_MEDIUM</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -17712,12 +17707,12 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Mandarin (official), Cantonese, local dialects</t>
+          <t>CHINESE_MANDARIN;CHINESE_CANTONESE</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>Medium to High</t>
+          <t>MEDIUM_HIGH</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -17771,7 +17766,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -17887,12 +17882,12 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Estonian (official), Russian</t>
+          <t>ESTONIAN;RUSSIAN</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>VERY_HIGH</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -17946,7 +17941,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -18062,12 +18057,12 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Greek (official), Turkish (official), English widely spoken</t>
+          <t>GREEK;TURKISH;ENGLISH</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -18121,7 +18116,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -18227,7 +18222,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>ARABIC</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -18254,7 +18249,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Uzbek</t>
+          <t>UZBEK</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
